--- a/output/version3/test/20-15/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
+++ b/output/version3/test/20-15/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1210</v>
+        <v>802</v>
       </c>
       <c r="C2" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1039</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1022</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1068</v>
+      </c>
+      <c r="H2" t="n">
         <v>912</v>
       </c>
-      <c r="D2" t="n">
-        <v>834</v>
-      </c>
-      <c r="E2" t="n">
-        <v>921</v>
-      </c>
-      <c r="F2" t="n">
-        <v>749</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1016</v>
-      </c>
-      <c r="H2" t="n">
-        <v>942</v>
-      </c>
       <c r="I2" t="n">
-        <v>961</v>
+        <v>1073</v>
       </c>
       <c r="J2" t="n">
-        <v>919</v>
+        <v>842</v>
       </c>
       <c r="K2" t="n">
-        <v>1039</v>
+        <v>836</v>
       </c>
       <c r="L2" t="n">
-        <v>950.3</v>
+        <v>967.1</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>1150</v>
+        <v>982</v>
       </c>
       <c r="C3" t="n">
-        <v>897</v>
+        <v>1230</v>
       </c>
       <c r="D3" t="n">
-        <v>919</v>
+        <v>1241</v>
       </c>
       <c r="E3" t="n">
-        <v>983</v>
+        <v>1040</v>
       </c>
       <c r="F3" t="n">
-        <v>986</v>
+        <v>885</v>
       </c>
       <c r="G3" t="n">
-        <v>1150</v>
+        <v>1017</v>
       </c>
       <c r="H3" t="n">
-        <v>963</v>
+        <v>943</v>
       </c>
       <c r="I3" t="n">
-        <v>952</v>
+        <v>876</v>
       </c>
       <c r="J3" t="n">
-        <v>828</v>
+        <v>924</v>
       </c>
       <c r="K3" t="n">
-        <v>1067</v>
+        <v>945</v>
       </c>
       <c r="L3" t="n">
-        <v>989.5</v>
+        <v>1008.3</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>1111</v>
+        <v>964</v>
       </c>
       <c r="C4" t="n">
-        <v>1037</v>
+        <v>839</v>
       </c>
       <c r="D4" t="n">
-        <v>1023</v>
+        <v>1088</v>
       </c>
       <c r="E4" t="n">
-        <v>899</v>
+        <v>854</v>
       </c>
       <c r="F4" t="n">
-        <v>1018</v>
+        <v>867</v>
       </c>
       <c r="G4" t="n">
-        <v>942</v>
+        <v>1010</v>
       </c>
       <c r="H4" t="n">
-        <v>1081</v>
+        <v>916</v>
       </c>
       <c r="I4" t="n">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J4" t="n">
-        <v>976</v>
+        <v>901</v>
       </c>
       <c r="K4" t="n">
-        <v>1135</v>
+        <v>1020</v>
       </c>
       <c r="L4" t="n">
-        <v>1021.7</v>
+        <v>945.3</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1019</v>
+        <v>1145</v>
       </c>
       <c r="C5" t="n">
-        <v>830</v>
+        <v>805</v>
       </c>
       <c r="D5" t="n">
+        <v>1049</v>
+      </c>
+      <c r="E5" t="n">
         <v>912</v>
       </c>
-      <c r="E5" t="n">
-        <v>889</v>
-      </c>
       <c r="F5" t="n">
-        <v>906</v>
+        <v>1084</v>
       </c>
       <c r="G5" t="n">
-        <v>873</v>
+        <v>936</v>
       </c>
       <c r="H5" t="n">
+        <v>916</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1052</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1020</v>
+      </c>
+      <c r="K5" t="n">
         <v>836</v>
       </c>
-      <c r="I5" t="n">
-        <v>930</v>
-      </c>
-      <c r="J5" t="n">
-        <v>843</v>
-      </c>
-      <c r="K5" t="n">
-        <v>871</v>
-      </c>
       <c r="L5" t="n">
-        <v>890.9</v>
+        <v>975.5</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>823</v>
+        <v>745</v>
       </c>
       <c r="C6" t="n">
-        <v>775</v>
+        <v>864</v>
       </c>
       <c r="D6" t="n">
-        <v>890</v>
+        <v>782</v>
       </c>
       <c r="E6" t="n">
-        <v>802</v>
+        <v>742</v>
       </c>
       <c r="F6" t="n">
-        <v>1011</v>
+        <v>728</v>
       </c>
       <c r="G6" t="n">
-        <v>869</v>
+        <v>945</v>
       </c>
       <c r="H6" t="n">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="I6" t="n">
-        <v>737</v>
+        <v>881</v>
       </c>
       <c r="J6" t="n">
-        <v>720</v>
+        <v>877</v>
       </c>
       <c r="K6" t="n">
-        <v>922</v>
+        <v>972</v>
       </c>
       <c r="L6" t="n">
-        <v>830.5</v>
+        <v>830.6</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="C7" t="n">
-        <v>1044</v>
+        <v>905</v>
       </c>
       <c r="D7" t="n">
-        <v>966</v>
+        <v>1090</v>
       </c>
       <c r="E7" t="n">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="F7" t="n">
-        <v>927</v>
+        <v>968</v>
       </c>
       <c r="G7" t="n">
-        <v>999</v>
+        <v>976</v>
       </c>
       <c r="H7" t="n">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="I7" t="n">
-        <v>874</v>
+        <v>1162</v>
       </c>
       <c r="J7" t="n">
-        <v>962</v>
+        <v>861</v>
       </c>
       <c r="K7" t="n">
-        <v>742</v>
+        <v>852</v>
       </c>
       <c r="L7" t="n">
-        <v>923.9</v>
+        <v>956.2</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>932</v>
+        <v>876</v>
       </c>
       <c r="C8" t="n">
-        <v>805</v>
+        <v>981</v>
       </c>
       <c r="D8" t="n">
-        <v>944</v>
+        <v>915</v>
       </c>
       <c r="E8" t="n">
-        <v>1003</v>
+        <v>913</v>
       </c>
       <c r="F8" t="n">
-        <v>891</v>
+        <v>953</v>
       </c>
       <c r="G8" t="n">
-        <v>960</v>
+        <v>941</v>
       </c>
       <c r="H8" t="n">
-        <v>866</v>
+        <v>1043</v>
       </c>
       <c r="I8" t="n">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="J8" t="n">
-        <v>1024</v>
+        <v>929</v>
       </c>
       <c r="K8" t="n">
-        <v>861</v>
+        <v>1021</v>
       </c>
       <c r="L8" t="n">
-        <v>928.5</v>
+        <v>957</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1038</v>
+        <v>1084</v>
       </c>
       <c r="C9" t="n">
-        <v>932</v>
+        <v>1046</v>
       </c>
       <c r="D9" t="n">
-        <v>989</v>
+        <v>1055</v>
       </c>
       <c r="E9" t="n">
-        <v>967</v>
+        <v>936</v>
       </c>
       <c r="F9" t="n">
-        <v>1023</v>
+        <v>908</v>
       </c>
       <c r="G9" t="n">
-        <v>908</v>
+        <v>846</v>
       </c>
       <c r="H9" t="n">
-        <v>956</v>
+        <v>1053</v>
       </c>
       <c r="I9" t="n">
-        <v>1005</v>
+        <v>714</v>
       </c>
       <c r="J9" t="n">
-        <v>810</v>
+        <v>1077</v>
       </c>
       <c r="K9" t="n">
-        <v>993</v>
+        <v>851</v>
       </c>
       <c r="L9" t="n">
-        <v>962.1</v>
+        <v>957</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>929</v>
+        <v>876</v>
       </c>
       <c r="C10" t="n">
-        <v>786</v>
+        <v>957</v>
       </c>
       <c r="D10" t="n">
-        <v>933</v>
+        <v>970</v>
       </c>
       <c r="E10" t="n">
-        <v>1098</v>
+        <v>943</v>
       </c>
       <c r="F10" t="n">
-        <v>805</v>
+        <v>920</v>
       </c>
       <c r="G10" t="n">
-        <v>831</v>
+        <v>990</v>
       </c>
       <c r="H10" t="n">
-        <v>1064</v>
+        <v>1048</v>
       </c>
       <c r="I10" t="n">
-        <v>862</v>
+        <v>962</v>
       </c>
       <c r="J10" t="n">
-        <v>761</v>
+        <v>957</v>
       </c>
       <c r="K10" t="n">
-        <v>852</v>
+        <v>927</v>
       </c>
       <c r="L10" t="n">
-        <v>892.1</v>
+        <v>955</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>849</v>
+        <v>1063</v>
       </c>
       <c r="C11" t="n">
-        <v>845</v>
+        <v>944</v>
       </c>
       <c r="D11" t="n">
-        <v>965</v>
+        <v>1012</v>
       </c>
       <c r="E11" t="n">
-        <v>1042</v>
+        <v>1010</v>
       </c>
       <c r="F11" t="n">
-        <v>803</v>
+        <v>972</v>
       </c>
       <c r="G11" t="n">
-        <v>925</v>
+        <v>980</v>
       </c>
       <c r="H11" t="n">
-        <v>1016</v>
+        <v>1100</v>
       </c>
       <c r="I11" t="n">
-        <v>1006</v>
+        <v>982</v>
       </c>
       <c r="J11" t="n">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="K11" t="n">
-        <v>1007</v>
+        <v>890</v>
       </c>
       <c r="L11" t="n">
-        <v>946</v>
+        <v>996.6</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1108</v>
+        <v>1173</v>
       </c>
       <c r="C12" t="n">
-        <v>1035</v>
+        <v>1128</v>
       </c>
       <c r="D12" t="n">
-        <v>1254</v>
+        <v>1076</v>
       </c>
       <c r="E12" t="n">
-        <v>1007</v>
+        <v>1062</v>
       </c>
       <c r="F12" t="n">
-        <v>1147</v>
+        <v>1021</v>
       </c>
       <c r="G12" t="n">
-        <v>1181</v>
+        <v>1144</v>
       </c>
       <c r="H12" t="n">
-        <v>1136</v>
+        <v>917</v>
       </c>
       <c r="I12" t="n">
-        <v>1226</v>
+        <v>1038</v>
       </c>
       <c r="J12" t="n">
-        <v>855</v>
+        <v>1027</v>
       </c>
       <c r="K12" t="n">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="L12" t="n">
-        <v>1109.2</v>
+        <v>1073.4</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>940</v>
+        <v>787</v>
       </c>
       <c r="C13" t="n">
-        <v>769</v>
+        <v>1017</v>
       </c>
       <c r="D13" t="n">
-        <v>976</v>
+        <v>923</v>
       </c>
       <c r="E13" t="n">
-        <v>765</v>
+        <v>832</v>
       </c>
       <c r="F13" t="n">
-        <v>731</v>
+        <v>1034</v>
       </c>
       <c r="G13" t="n">
-        <v>753</v>
+        <v>831</v>
       </c>
       <c r="H13" t="n">
-        <v>946</v>
+        <v>1126</v>
       </c>
       <c r="I13" t="n">
-        <v>846</v>
+        <v>1032</v>
       </c>
       <c r="J13" t="n">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="K13" t="n">
-        <v>838</v>
+        <v>876</v>
       </c>
       <c r="L13" t="n">
-        <v>841.4</v>
+        <v>931.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>1049</v>
+        <v>1126</v>
       </c>
       <c r="C14" t="n">
-        <v>1060</v>
+        <v>1041</v>
       </c>
       <c r="D14" t="n">
-        <v>1022</v>
+        <v>908</v>
       </c>
       <c r="E14" t="n">
-        <v>1091</v>
+        <v>890</v>
       </c>
       <c r="F14" t="n">
-        <v>1101</v>
+        <v>861</v>
       </c>
       <c r="G14" t="n">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="H14" t="n">
-        <v>1004</v>
+        <v>836</v>
       </c>
       <c r="I14" t="n">
-        <v>968</v>
+        <v>942</v>
       </c>
       <c r="J14" t="n">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="K14" t="n">
-        <v>1138</v>
+        <v>874</v>
       </c>
       <c r="L14" t="n">
-        <v>1023.6</v>
+        <v>930.5</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>967</v>
+        <v>895</v>
       </c>
       <c r="C15" t="n">
-        <v>825</v>
+        <v>871</v>
       </c>
       <c r="D15" t="n">
-        <v>882</v>
+        <v>1156</v>
       </c>
       <c r="E15" t="n">
-        <v>937</v>
+        <v>974</v>
       </c>
       <c r="F15" t="n">
-        <v>902</v>
+        <v>779</v>
       </c>
       <c r="G15" t="n">
-        <v>916</v>
+        <v>1154</v>
       </c>
       <c r="H15" t="n">
         <v>792</v>
       </c>
       <c r="I15" t="n">
-        <v>1070</v>
+        <v>972</v>
       </c>
       <c r="J15" t="n">
-        <v>922</v>
+        <v>841</v>
       </c>
       <c r="K15" t="n">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="L15" t="n">
-        <v>901.4</v>
+        <v>925.5</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>931</v>
+        <v>1115</v>
       </c>
       <c r="C16" t="n">
-        <v>935</v>
+        <v>918</v>
       </c>
       <c r="D16" t="n">
-        <v>1001</v>
+        <v>1039</v>
       </c>
       <c r="E16" t="n">
-        <v>1070</v>
+        <v>1029</v>
       </c>
       <c r="F16" t="n">
-        <v>983</v>
+        <v>907</v>
       </c>
       <c r="G16" t="n">
-        <v>931</v>
+        <v>907</v>
       </c>
       <c r="H16" t="n">
-        <v>1014</v>
+        <v>1053</v>
       </c>
       <c r="I16" t="n">
-        <v>1006</v>
+        <v>1059</v>
       </c>
       <c r="J16" t="n">
-        <v>1021</v>
+        <v>970</v>
       </c>
       <c r="K16" t="n">
-        <v>1028</v>
+        <v>959</v>
       </c>
       <c r="L16" t="n">
-        <v>992</v>
+        <v>995.6</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>1071</v>
+        <v>1093</v>
       </c>
       <c r="C17" t="n">
-        <v>934</v>
+        <v>1137</v>
       </c>
       <c r="D17" t="n">
-        <v>1151</v>
+        <v>923</v>
       </c>
       <c r="E17" t="n">
-        <v>956</v>
+        <v>1061</v>
       </c>
       <c r="F17" t="n">
         <v>1137</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>895</v>
       </c>
       <c r="H17" t="n">
-        <v>968</v>
+        <v>877</v>
       </c>
       <c r="I17" t="n">
-        <v>1072</v>
+        <v>1110</v>
       </c>
       <c r="J17" t="n">
-        <v>1009</v>
+        <v>1065</v>
       </c>
       <c r="K17" t="n">
-        <v>1209</v>
+        <v>888</v>
       </c>
       <c r="L17" t="n">
-        <v>1050.7</v>
+        <v>1018.6</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>1148</v>
+        <v>924</v>
       </c>
       <c r="C18" t="n">
-        <v>1218</v>
+        <v>910</v>
       </c>
       <c r="D18" t="n">
-        <v>980</v>
+        <v>1168</v>
       </c>
       <c r="E18" t="n">
-        <v>982</v>
+        <v>923</v>
       </c>
       <c r="F18" t="n">
-        <v>1196</v>
+        <v>1047</v>
       </c>
       <c r="G18" t="n">
-        <v>1063</v>
+        <v>1115</v>
       </c>
       <c r="H18" t="n">
-        <v>1108</v>
+        <v>932</v>
       </c>
       <c r="I18" t="n">
-        <v>1061</v>
+        <v>967</v>
       </c>
       <c r="J18" t="n">
-        <v>835</v>
+        <v>865</v>
       </c>
       <c r="K18" t="n">
-        <v>1017</v>
+        <v>977</v>
       </c>
       <c r="L18" t="n">
-        <v>1060.8</v>
+        <v>982.8</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>1028</v>
+        <v>795</v>
       </c>
       <c r="C19" t="n">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D19" t="n">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="E19" t="n">
-        <v>905</v>
+        <v>747</v>
       </c>
       <c r="F19" t="n">
-        <v>764</v>
+        <v>864</v>
       </c>
       <c r="G19" t="n">
-        <v>860</v>
+        <v>986</v>
       </c>
       <c r="H19" t="n">
-        <v>866</v>
+        <v>1029</v>
       </c>
       <c r="I19" t="n">
-        <v>843</v>
+        <v>966</v>
       </c>
       <c r="J19" t="n">
-        <v>845</v>
+        <v>912</v>
       </c>
       <c r="K19" t="n">
-        <v>926</v>
+        <v>1018</v>
       </c>
       <c r="L19" t="n">
-        <v>874.2</v>
+        <v>901.1</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>1158</v>
+        <v>1175</v>
       </c>
       <c r="C20" t="n">
-        <v>974</v>
+        <v>1167</v>
       </c>
       <c r="D20" t="n">
-        <v>870</v>
+        <v>1010</v>
       </c>
       <c r="E20" t="n">
-        <v>901</v>
+        <v>973</v>
       </c>
       <c r="F20" t="n">
-        <v>1038</v>
+        <v>1006</v>
       </c>
       <c r="G20" t="n">
-        <v>922</v>
+        <v>1113</v>
       </c>
       <c r="H20" t="n">
-        <v>1117</v>
+        <v>1017</v>
       </c>
       <c r="I20" t="n">
-        <v>1193</v>
+        <v>1129</v>
       </c>
       <c r="J20" t="n">
-        <v>968</v>
+        <v>1008</v>
       </c>
       <c r="K20" t="n">
-        <v>1155</v>
+        <v>978</v>
       </c>
       <c r="L20" t="n">
-        <v>1029.6</v>
+        <v>1057.6</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="C21" t="n">
-        <v>869</v>
+        <v>990</v>
       </c>
       <c r="D21" t="n">
-        <v>823</v>
+        <v>1057</v>
       </c>
       <c r="E21" t="n">
-        <v>954</v>
+        <v>936</v>
       </c>
       <c r="F21" t="n">
-        <v>945</v>
+        <v>765</v>
       </c>
       <c r="G21" t="n">
-        <v>852</v>
+        <v>1070</v>
       </c>
       <c r="H21" t="n">
-        <v>991</v>
+        <v>870</v>
       </c>
       <c r="I21" t="n">
-        <v>1034</v>
+        <v>921</v>
       </c>
       <c r="J21" t="n">
-        <v>899</v>
+        <v>1015</v>
       </c>
       <c r="K21" t="n">
-        <v>877</v>
+        <v>975</v>
       </c>
       <c r="L21" t="n">
-        <v>928.2</v>
+        <v>962.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>908</v>
+        <v>854</v>
       </c>
       <c r="C22" t="n">
-        <v>835</v>
+        <v>958</v>
       </c>
       <c r="D22" t="n">
-        <v>914</v>
+        <v>813</v>
       </c>
       <c r="E22" t="n">
-        <v>905</v>
+        <v>841</v>
       </c>
       <c r="F22" t="n">
-        <v>886</v>
+        <v>865</v>
       </c>
       <c r="G22" t="n">
-        <v>945</v>
+        <v>893</v>
       </c>
       <c r="H22" t="n">
-        <v>780</v>
+        <v>826</v>
       </c>
       <c r="I22" t="n">
-        <v>874</v>
+        <v>1029</v>
       </c>
       <c r="J22" t="n">
-        <v>814</v>
+        <v>1057</v>
       </c>
       <c r="K22" t="n">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="L22" t="n">
-        <v>864.9</v>
+        <v>893.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>941</v>
+        <v>1033</v>
       </c>
       <c r="C23" t="n">
-        <v>998</v>
+        <v>1120</v>
       </c>
       <c r="D23" t="n">
-        <v>1203</v>
+        <v>1147</v>
       </c>
       <c r="E23" t="n">
-        <v>1133</v>
+        <v>937</v>
       </c>
       <c r="F23" t="n">
-        <v>1142</v>
+        <v>1183</v>
       </c>
       <c r="G23" t="n">
-        <v>996</v>
+        <v>1083</v>
       </c>
       <c r="H23" t="n">
-        <v>878</v>
+        <v>1098</v>
       </c>
       <c r="I23" t="n">
-        <v>1067</v>
+        <v>1181</v>
       </c>
       <c r="J23" t="n">
-        <v>1005</v>
+        <v>1115</v>
       </c>
       <c r="K23" t="n">
-        <v>948</v>
+        <v>1187</v>
       </c>
       <c r="L23" t="n">
-        <v>1031.1</v>
+        <v>1108.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>1221</v>
+        <v>1038</v>
       </c>
       <c r="C24" t="n">
-        <v>1111</v>
+        <v>1074</v>
       </c>
       <c r="D24" t="n">
-        <v>983</v>
+        <v>1063</v>
       </c>
       <c r="E24" t="n">
-        <v>1300</v>
+        <v>1130</v>
       </c>
       <c r="F24" t="n">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="G24" t="n">
-        <v>1007</v>
+        <v>1173</v>
       </c>
       <c r="H24" t="n">
-        <v>920</v>
+        <v>1130</v>
       </c>
       <c r="I24" t="n">
+        <v>1163</v>
+      </c>
+      <c r="J24" t="n">
         <v>1031</v>
       </c>
-      <c r="J24" t="n">
-        <v>856</v>
-      </c>
       <c r="K24" t="n">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="L24" t="n">
-        <v>1054.6</v>
+        <v>1091.6</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>1131</v>
+        <v>1083</v>
       </c>
       <c r="C25" t="n">
-        <v>1021</v>
+        <v>899</v>
       </c>
       <c r="D25" t="n">
-        <v>970</v>
+        <v>845</v>
       </c>
       <c r="E25" t="n">
-        <v>1044</v>
+        <v>843</v>
       </c>
       <c r="F25" t="n">
-        <v>911</v>
+        <v>989</v>
       </c>
       <c r="G25" t="n">
-        <v>1035</v>
+        <v>1099</v>
       </c>
       <c r="H25" t="n">
-        <v>996</v>
+        <v>947</v>
       </c>
       <c r="I25" t="n">
-        <v>917</v>
+        <v>1041</v>
       </c>
       <c r="J25" t="n">
-        <v>1168</v>
+        <v>1059</v>
       </c>
       <c r="K25" t="n">
-        <v>992</v>
+        <v>908</v>
       </c>
       <c r="L25" t="n">
-        <v>1018.5</v>
+        <v>971.3</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>1001</v>
+        <v>852</v>
       </c>
       <c r="C26" t="n">
-        <v>886</v>
+        <v>1010</v>
       </c>
       <c r="D26" t="n">
-        <v>877</v>
+        <v>745</v>
       </c>
       <c r="E26" t="n">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="F26" t="n">
-        <v>820</v>
+        <v>908</v>
       </c>
       <c r="G26" t="n">
-        <v>1190</v>
+        <v>837</v>
       </c>
       <c r="H26" t="n">
-        <v>1123</v>
+        <v>1047</v>
       </c>
       <c r="I26" t="n">
-        <v>928</v>
+        <v>776</v>
       </c>
       <c r="J26" t="n">
-        <v>860</v>
+        <v>837</v>
       </c>
       <c r="K26" t="n">
-        <v>1013</v>
+        <v>1072</v>
       </c>
       <c r="L26" t="n">
-        <v>960.7</v>
+        <v>898.3</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>1007</v>
+        <v>933</v>
       </c>
       <c r="C27" t="n">
-        <v>1203</v>
+        <v>1127</v>
       </c>
       <c r="D27" t="n">
-        <v>1102</v>
+        <v>1003</v>
       </c>
       <c r="E27" t="n">
-        <v>937</v>
+        <v>868</v>
       </c>
       <c r="F27" t="n">
-        <v>970</v>
+        <v>1034</v>
       </c>
       <c r="G27" t="n">
-        <v>926</v>
+        <v>1101</v>
       </c>
       <c r="H27" t="n">
-        <v>1024</v>
+        <v>1031</v>
       </c>
       <c r="I27" t="n">
-        <v>1060</v>
+        <v>1141</v>
       </c>
       <c r="J27" t="n">
-        <v>1136</v>
+        <v>843</v>
       </c>
       <c r="K27" t="n">
-        <v>997</v>
+        <v>954</v>
       </c>
       <c r="L27" t="n">
-        <v>1036.2</v>
+        <v>1003.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>1179</v>
+        <v>1090</v>
       </c>
       <c r="C28" t="n">
-        <v>983</v>
+        <v>1063</v>
       </c>
       <c r="D28" t="n">
-        <v>1031</v>
+        <v>1155</v>
       </c>
       <c r="E28" t="n">
-        <v>1104</v>
+        <v>1082</v>
       </c>
       <c r="F28" t="n">
-        <v>1059</v>
+        <v>927</v>
       </c>
       <c r="G28" t="n">
-        <v>1264</v>
+        <v>874</v>
       </c>
       <c r="H28" t="n">
-        <v>1098</v>
+        <v>1042</v>
       </c>
       <c r="I28" t="n">
-        <v>1010</v>
+        <v>959</v>
       </c>
       <c r="J28" t="n">
-        <v>1073</v>
+        <v>1126</v>
       </c>
       <c r="K28" t="n">
-        <v>1025</v>
+        <v>890</v>
       </c>
       <c r="L28" t="n">
-        <v>1082.6</v>
+        <v>1020.8</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>783</v>
+        <v>1002</v>
       </c>
       <c r="C29" t="n">
-        <v>1034</v>
+        <v>1010</v>
       </c>
       <c r="D29" t="n">
-        <v>1036</v>
+        <v>1099</v>
       </c>
       <c r="E29" t="n">
-        <v>953</v>
+        <v>965</v>
       </c>
       <c r="F29" t="n">
-        <v>942</v>
+        <v>1022</v>
       </c>
       <c r="G29" t="n">
-        <v>1080</v>
+        <v>1007</v>
       </c>
       <c r="H29" t="n">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="I29" t="n">
-        <v>940</v>
+        <v>1121</v>
       </c>
       <c r="J29" t="n">
-        <v>795</v>
+        <v>1007</v>
       </c>
       <c r="K29" t="n">
-        <v>1107</v>
+        <v>972</v>
       </c>
       <c r="L29" t="n">
-        <v>967</v>
+        <v>1021.3</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>1177</v>
+        <v>1146</v>
       </c>
       <c r="C30" t="n">
-        <v>1056</v>
+        <v>947</v>
       </c>
       <c r="D30" t="n">
-        <v>958</v>
+        <v>865</v>
       </c>
       <c r="E30" t="n">
-        <v>952</v>
+        <v>987</v>
       </c>
       <c r="F30" t="n">
-        <v>956</v>
+        <v>991</v>
       </c>
       <c r="G30" t="n">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="H30" t="n">
-        <v>877</v>
+        <v>1009</v>
       </c>
       <c r="I30" t="n">
-        <v>1089</v>
+        <v>1068</v>
       </c>
       <c r="J30" t="n">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="K30" t="n">
-        <v>1170</v>
+        <v>1022</v>
       </c>
       <c r="L30" t="n">
-        <v>1039.3</v>
+        <v>1020.2</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>876</v>
+        <v>1078</v>
       </c>
       <c r="C31" t="n">
-        <v>1054</v>
+        <v>757</v>
       </c>
       <c r="D31" t="n">
-        <v>852</v>
+        <v>1040</v>
       </c>
       <c r="E31" t="n">
-        <v>969</v>
+        <v>998</v>
       </c>
       <c r="F31" t="n">
-        <v>916</v>
+        <v>985</v>
       </c>
       <c r="G31" t="n">
-        <v>926</v>
+        <v>932</v>
       </c>
       <c r="H31" t="n">
-        <v>1023</v>
+        <v>979</v>
       </c>
       <c r="I31" t="n">
-        <v>892</v>
+        <v>952</v>
       </c>
       <c r="J31" t="n">
-        <v>1079</v>
+        <v>984</v>
       </c>
       <c r="K31" t="n">
-        <v>1067</v>
+        <v>872</v>
       </c>
       <c r="L31" t="n">
-        <v>965.4</v>
+        <v>957.7</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1088</v>
+        <v>920</v>
       </c>
       <c r="C32" t="n">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D32" t="n">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E32" t="n">
-        <v>1081</v>
+        <v>1009</v>
       </c>
       <c r="F32" t="n">
-        <v>939</v>
+        <v>1044</v>
       </c>
       <c r="G32" t="n">
-        <v>908</v>
+        <v>870</v>
       </c>
       <c r="H32" t="n">
-        <v>1134</v>
+        <v>1032</v>
       </c>
       <c r="I32" t="n">
-        <v>858</v>
+        <v>1086</v>
       </c>
       <c r="J32" t="n">
-        <v>781</v>
+        <v>931</v>
       </c>
       <c r="K32" t="n">
-        <v>868</v>
+        <v>1080</v>
       </c>
       <c r="L32" t="n">
-        <v>952.1</v>
+        <v>983.1</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>1079</v>
+        <v>1046</v>
       </c>
       <c r="C33" t="n">
-        <v>858</v>
+        <v>941</v>
       </c>
       <c r="D33" t="n">
-        <v>948</v>
+        <v>1054</v>
       </c>
       <c r="E33" t="n">
-        <v>843</v>
+        <v>985</v>
       </c>
       <c r="F33" t="n">
-        <v>901</v>
+        <v>952</v>
       </c>
       <c r="G33" t="n">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="H33" t="n">
-        <v>918</v>
+        <v>944</v>
       </c>
       <c r="I33" t="n">
-        <v>1052</v>
+        <v>888</v>
       </c>
       <c r="J33" t="n">
-        <v>907</v>
+        <v>893</v>
       </c>
       <c r="K33" t="n">
-        <v>946</v>
+        <v>848</v>
       </c>
       <c r="L33" t="n">
-        <v>939.3</v>
+        <v>949</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>882</v>
+        <v>947</v>
       </c>
       <c r="C34" t="n">
-        <v>809</v>
+        <v>1050</v>
       </c>
       <c r="D34" t="n">
-        <v>908</v>
+        <v>876</v>
       </c>
       <c r="E34" t="n">
-        <v>965</v>
+        <v>1008</v>
       </c>
       <c r="F34" t="n">
-        <v>780</v>
+        <v>823</v>
       </c>
       <c r="G34" t="n">
-        <v>1161</v>
+        <v>960</v>
       </c>
       <c r="H34" t="n">
-        <v>824</v>
+        <v>960</v>
       </c>
       <c r="I34" t="n">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="J34" t="n">
-        <v>968</v>
+        <v>838</v>
       </c>
       <c r="K34" t="n">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="L34" t="n">
-        <v>900</v>
+        <v>916.5</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>1089</v>
+        <v>1032</v>
       </c>
       <c r="C35" t="n">
-        <v>874</v>
+        <v>802</v>
       </c>
       <c r="D35" t="n">
-        <v>976</v>
+        <v>868</v>
       </c>
       <c r="E35" t="n">
-        <v>1022</v>
+        <v>731</v>
       </c>
       <c r="F35" t="n">
-        <v>914</v>
+        <v>1032</v>
       </c>
       <c r="G35" t="n">
-        <v>856</v>
+        <v>1042</v>
       </c>
       <c r="H35" t="n">
-        <v>1009</v>
+        <v>894</v>
       </c>
       <c r="I35" t="n">
-        <v>1044</v>
+        <v>839</v>
       </c>
       <c r="J35" t="n">
-        <v>1021</v>
+        <v>1057</v>
       </c>
       <c r="K35" t="n">
-        <v>944</v>
+        <v>764</v>
       </c>
       <c r="L35" t="n">
-        <v>974.9</v>
+        <v>906.1</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1276</v>
+        <v>1145</v>
       </c>
       <c r="C36" t="n">
-        <v>977</v>
+        <v>1075</v>
       </c>
       <c r="D36" t="n">
-        <v>852</v>
+        <v>936</v>
       </c>
       <c r="E36" t="n">
-        <v>1164</v>
+        <v>1187</v>
       </c>
       <c r="F36" t="n">
-        <v>1243</v>
+        <v>1195</v>
       </c>
       <c r="G36" t="n">
-        <v>1022</v>
+        <v>1105</v>
       </c>
       <c r="H36" t="n">
-        <v>993</v>
+        <v>1009</v>
       </c>
       <c r="I36" t="n">
-        <v>1248</v>
+        <v>1144</v>
       </c>
       <c r="J36" t="n">
-        <v>1002</v>
+        <v>873</v>
       </c>
       <c r="K36" t="n">
-        <v>1106</v>
+        <v>885</v>
       </c>
       <c r="L36" t="n">
-        <v>1088.3</v>
+        <v>1055.4</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="C37" t="n">
-        <v>744</v>
+        <v>947</v>
       </c>
       <c r="D37" t="n">
+        <v>786</v>
+      </c>
+      <c r="E37" t="n">
+        <v>823</v>
+      </c>
+      <c r="F37" t="n">
+        <v>781</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1084</v>
+      </c>
+      <c r="H37" t="n">
+        <v>829</v>
+      </c>
+      <c r="I37" t="n">
         <v>936</v>
       </c>
-      <c r="E37" t="n">
-        <v>875</v>
-      </c>
-      <c r="F37" t="n">
-        <v>957</v>
-      </c>
-      <c r="G37" t="n">
-        <v>812</v>
-      </c>
-      <c r="H37" t="n">
-        <v>901</v>
-      </c>
-      <c r="I37" t="n">
-        <v>830</v>
-      </c>
       <c r="J37" t="n">
-        <v>776</v>
+        <v>919</v>
       </c>
       <c r="K37" t="n">
-        <v>1029</v>
+        <v>874</v>
       </c>
       <c r="L37" t="n">
-        <v>875.1</v>
+        <v>886.5</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>1009</v>
+        <v>1052</v>
       </c>
       <c r="C38" t="n">
-        <v>1036</v>
+        <v>884</v>
       </c>
       <c r="D38" t="n">
-        <v>821</v>
+        <v>847</v>
       </c>
       <c r="E38" t="n">
-        <v>916</v>
+        <v>1082</v>
       </c>
       <c r="F38" t="n">
-        <v>1116</v>
+        <v>957</v>
       </c>
       <c r="G38" t="n">
-        <v>1065</v>
+        <v>1176</v>
       </c>
       <c r="H38" t="n">
-        <v>972</v>
+        <v>921</v>
       </c>
       <c r="I38" t="n">
-        <v>1042</v>
+        <v>1093</v>
       </c>
       <c r="J38" t="n">
-        <v>1084</v>
+        <v>927</v>
       </c>
       <c r="K38" t="n">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="L38" t="n">
-        <v>1006</v>
+        <v>995.9</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>950</v>
+        <v>914</v>
       </c>
       <c r="C39" t="n">
-        <v>1012</v>
+        <v>1044</v>
       </c>
       <c r="D39" t="n">
-        <v>906</v>
+        <v>798</v>
       </c>
       <c r="E39" t="n">
-        <v>1071</v>
+        <v>978</v>
       </c>
       <c r="F39" t="n">
-        <v>786</v>
+        <v>879</v>
       </c>
       <c r="G39" t="n">
-        <v>932</v>
+        <v>848</v>
       </c>
       <c r="H39" t="n">
-        <v>940</v>
+        <v>1114</v>
       </c>
       <c r="I39" t="n">
-        <v>790</v>
+        <v>909</v>
       </c>
       <c r="J39" t="n">
-        <v>842</v>
+        <v>1051</v>
       </c>
       <c r="K39" t="n">
-        <v>1037</v>
+        <v>925</v>
       </c>
       <c r="L39" t="n">
-        <v>926.6</v>
+        <v>946</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>1131</v>
+        <v>916</v>
       </c>
       <c r="C40" t="n">
-        <v>983</v>
+        <v>873</v>
       </c>
       <c r="D40" t="n">
+        <v>1134</v>
+      </c>
+      <c r="E40" t="n">
+        <v>817</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1103</v>
+      </c>
+      <c r="G40" t="n">
+        <v>895</v>
+      </c>
+      <c r="H40" t="n">
+        <v>824</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1024</v>
+      </c>
+      <c r="J40" t="n">
         <v>1110</v>
       </c>
-      <c r="E40" t="n">
-        <v>979</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1018</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1011</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1015</v>
-      </c>
-      <c r="I40" t="n">
-        <v>893</v>
-      </c>
-      <c r="J40" t="n">
-        <v>849</v>
-      </c>
       <c r="K40" t="n">
-        <v>1027</v>
+        <v>969</v>
       </c>
       <c r="L40" t="n">
-        <v>1001.6</v>
+        <v>966.5</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>953</v>
+        <v>1042</v>
       </c>
       <c r="C41" t="n">
-        <v>961</v>
+        <v>922</v>
       </c>
       <c r="D41" t="n">
-        <v>1139</v>
+        <v>941</v>
       </c>
       <c r="E41" t="n">
-        <v>847</v>
+        <v>977</v>
       </c>
       <c r="F41" t="n">
-        <v>1066</v>
+        <v>1022</v>
       </c>
       <c r="G41" t="n">
-        <v>1006</v>
+        <v>902</v>
       </c>
       <c r="H41" t="n">
-        <v>1016</v>
+        <v>1088</v>
       </c>
       <c r="I41" t="n">
-        <v>957</v>
+        <v>806</v>
       </c>
       <c r="J41" t="n">
-        <v>1166</v>
+        <v>991</v>
       </c>
       <c r="K41" t="n">
-        <v>931</v>
+        <v>1063</v>
       </c>
       <c r="L41" t="n">
-        <v>1004.2</v>
+        <v>975.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>792</v>
+        <v>862</v>
       </c>
       <c r="C42" t="n">
-        <v>897</v>
+        <v>989</v>
       </c>
       <c r="D42" t="n">
-        <v>794</v>
+        <v>953</v>
       </c>
       <c r="E42" t="n">
-        <v>948</v>
+        <v>1124</v>
       </c>
       <c r="F42" t="n">
-        <v>727</v>
+        <v>945</v>
       </c>
       <c r="G42" t="n">
-        <v>871</v>
+        <v>1130</v>
       </c>
       <c r="H42" t="n">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="I42" t="n">
-        <v>755</v>
+        <v>912</v>
       </c>
       <c r="J42" t="n">
-        <v>731</v>
+        <v>813</v>
       </c>
       <c r="K42" t="n">
-        <v>798</v>
+        <v>919</v>
       </c>
       <c r="L42" t="n">
-        <v>812</v>
+        <v>946.8</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>947</v>
+        <v>773</v>
       </c>
       <c r="C43" t="n">
-        <v>906</v>
+        <v>1077</v>
       </c>
       <c r="D43" t="n">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="E43" t="n">
-        <v>1050</v>
+        <v>1011</v>
       </c>
       <c r="F43" t="n">
-        <v>1031</v>
+        <v>1055</v>
       </c>
       <c r="G43" t="n">
-        <v>957</v>
+        <v>1033</v>
       </c>
       <c r="H43" t="n">
-        <v>889</v>
+        <v>780</v>
       </c>
       <c r="I43" t="n">
-        <v>883</v>
+        <v>998</v>
       </c>
       <c r="J43" t="n">
-        <v>905</v>
+        <v>1016</v>
       </c>
       <c r="K43" t="n">
-        <v>906</v>
+        <v>949</v>
       </c>
       <c r="L43" t="n">
-        <v>940.2</v>
+        <v>964</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>935</v>
+        <v>1109</v>
       </c>
       <c r="C44" t="n">
-        <v>883</v>
+        <v>792</v>
       </c>
       <c r="D44" t="n">
-        <v>849</v>
+        <v>842</v>
       </c>
       <c r="E44" t="n">
-        <v>848</v>
+        <v>924</v>
       </c>
       <c r="F44" t="n">
-        <v>912</v>
+        <v>1128</v>
       </c>
       <c r="G44" t="n">
-        <v>1043</v>
+        <v>1016</v>
       </c>
       <c r="H44" t="n">
-        <v>911</v>
+        <v>928</v>
       </c>
       <c r="I44" t="n">
-        <v>799</v>
+        <v>1015</v>
       </c>
       <c r="J44" t="n">
-        <v>1083</v>
+        <v>844</v>
       </c>
       <c r="K44" t="n">
-        <v>999</v>
+        <v>858</v>
       </c>
       <c r="L44" t="n">
-        <v>926.2</v>
+        <v>945.6</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>942</v>
+        <v>1056</v>
       </c>
       <c r="C45" t="n">
-        <v>927</v>
+        <v>1017</v>
       </c>
       <c r="D45" t="n">
-        <v>964</v>
+        <v>1052</v>
       </c>
       <c r="E45" t="n">
-        <v>883</v>
+        <v>993</v>
       </c>
       <c r="F45" t="n">
-        <v>1028</v>
+        <v>1007</v>
       </c>
       <c r="G45" t="n">
         <v>939</v>
       </c>
       <c r="H45" t="n">
-        <v>905</v>
+        <v>1080</v>
       </c>
       <c r="I45" t="n">
-        <v>1080</v>
+        <v>1021</v>
       </c>
       <c r="J45" t="n">
-        <v>1048</v>
+        <v>982</v>
       </c>
       <c r="K45" t="n">
-        <v>1122</v>
+        <v>1047</v>
       </c>
       <c r="L45" t="n">
-        <v>983.8</v>
+        <v>1019.4</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1116</v>
+        <v>946</v>
       </c>
       <c r="C46" t="n">
-        <v>928</v>
+        <v>921</v>
       </c>
       <c r="D46" t="n">
-        <v>1067</v>
+        <v>1076</v>
       </c>
       <c r="E46" t="n">
-        <v>1007</v>
+        <v>883</v>
       </c>
       <c r="F46" t="n">
-        <v>989</v>
+        <v>936</v>
       </c>
       <c r="G46" t="n">
-        <v>872</v>
+        <v>1061</v>
       </c>
       <c r="H46" t="n">
-        <v>889</v>
+        <v>1022</v>
       </c>
       <c r="I46" t="n">
-        <v>989</v>
+        <v>951</v>
       </c>
       <c r="J46" t="n">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="K46" t="n">
-        <v>933</v>
+        <v>1001</v>
       </c>
       <c r="L46" t="n">
-        <v>983.2</v>
+        <v>982.8</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>1137</v>
+        <v>900</v>
       </c>
       <c r="C47" t="n">
-        <v>943</v>
+        <v>1047</v>
       </c>
       <c r="D47" t="n">
-        <v>1049</v>
+        <v>1017</v>
       </c>
       <c r="E47" t="n">
-        <v>985</v>
+        <v>977</v>
       </c>
       <c r="F47" t="n">
-        <v>1070</v>
+        <v>1115</v>
       </c>
       <c r="G47" t="n">
-        <v>1040</v>
+        <v>898</v>
       </c>
       <c r="H47" t="n">
-        <v>917</v>
+        <v>1062</v>
       </c>
       <c r="I47" t="n">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="J47" t="n">
-        <v>918</v>
+        <v>1046</v>
       </c>
       <c r="K47" t="n">
-        <v>1136</v>
+        <v>1053</v>
       </c>
       <c r="L47" t="n">
-        <v>1016.4</v>
+        <v>1008.7</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>1154</v>
+        <v>790</v>
       </c>
       <c r="C48" t="n">
-        <v>1006</v>
+        <v>892</v>
       </c>
       <c r="D48" t="n">
-        <v>941</v>
+        <v>1109</v>
       </c>
       <c r="E48" t="n">
-        <v>866</v>
+        <v>1045</v>
       </c>
       <c r="F48" t="n">
-        <v>1086</v>
+        <v>1044</v>
       </c>
       <c r="G48" t="n">
-        <v>997</v>
+        <v>1112</v>
       </c>
       <c r="H48" t="n">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="I48" t="n">
-        <v>834</v>
+        <v>857</v>
       </c>
       <c r="J48" t="n">
-        <v>1129</v>
+        <v>964</v>
       </c>
       <c r="K48" t="n">
-        <v>998</v>
+        <v>956</v>
       </c>
       <c r="L48" t="n">
-        <v>993.1</v>
+        <v>968.5</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>1057</v>
+        <v>1006</v>
       </c>
       <c r="C49" t="n">
-        <v>1002</v>
+        <v>1123</v>
       </c>
       <c r="D49" t="n">
-        <v>1111</v>
+        <v>908</v>
       </c>
       <c r="E49" t="n">
-        <v>1047</v>
+        <v>1062</v>
       </c>
       <c r="F49" t="n">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="G49" t="n">
-        <v>1156</v>
+        <v>902</v>
       </c>
       <c r="H49" t="n">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="I49" t="n">
-        <v>1007</v>
+        <v>944</v>
       </c>
       <c r="J49" t="n">
-        <v>907</v>
+        <v>1090</v>
       </c>
       <c r="K49" t="n">
-        <v>1066</v>
+        <v>1049</v>
       </c>
       <c r="L49" t="n">
-        <v>1036.2</v>
+        <v>1009.3</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>965</v>
+        <v>1018</v>
       </c>
       <c r="C50" t="n">
-        <v>1065</v>
+        <v>1021</v>
       </c>
       <c r="D50" t="n">
-        <v>1115</v>
+        <v>986</v>
       </c>
       <c r="E50" t="n">
-        <v>972</v>
+        <v>841</v>
       </c>
       <c r="F50" t="n">
-        <v>843</v>
+        <v>990</v>
       </c>
       <c r="G50" t="n">
-        <v>1086</v>
+        <v>1014</v>
       </c>
       <c r="H50" t="n">
-        <v>941</v>
+        <v>982</v>
       </c>
       <c r="I50" t="n">
-        <v>899</v>
+        <v>1058</v>
       </c>
       <c r="J50" t="n">
-        <v>836</v>
+        <v>917</v>
       </c>
       <c r="K50" t="n">
-        <v>928</v>
+        <v>1054</v>
       </c>
       <c r="L50" t="n">
-        <v>965</v>
+        <v>988.1</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>855</v>
+        <v>826</v>
       </c>
       <c r="C51" t="n">
-        <v>977</v>
+        <v>986</v>
       </c>
       <c r="D51" t="n">
-        <v>1059</v>
+        <v>897</v>
       </c>
       <c r="E51" t="n">
-        <v>1228</v>
+        <v>1079</v>
       </c>
       <c r="F51" t="n">
-        <v>1057</v>
+        <v>1100</v>
       </c>
       <c r="G51" t="n">
-        <v>926</v>
+        <v>1049</v>
       </c>
       <c r="H51" t="n">
-        <v>1131</v>
+        <v>978</v>
       </c>
       <c r="I51" t="n">
-        <v>1030</v>
+        <v>965</v>
       </c>
       <c r="J51" t="n">
-        <v>1159</v>
+        <v>951</v>
       </c>
       <c r="K51" t="n">
-        <v>948</v>
+        <v>1096</v>
       </c>
       <c r="L51" t="n">
-        <v>1037</v>
+        <v>992.7</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1017.48</v>
+        <v>977.02</v>
       </c>
       <c r="C52" t="n">
-        <v>942.54</v>
+        <v>976.72</v>
       </c>
       <c r="D52" t="n">
-        <v>972.52</v>
+        <v>983.54</v>
       </c>
       <c r="E52" t="n">
-        <v>978.08</v>
+        <v>956.84</v>
       </c>
       <c r="F52" t="n">
-        <v>962.9</v>
+        <v>975.1799999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>978.1</v>
+        <v>998.08</v>
       </c>
       <c r="H52" t="n">
-        <v>963.26</v>
+        <v>968.76</v>
       </c>
       <c r="I52" t="n">
-        <v>965.1799999999999</v>
+        <v>990.8200000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>939.3200000000001</v>
+        <v>965.08</v>
       </c>
       <c r="K52" t="n">
-        <v>986.24</v>
+        <v>952.12</v>
       </c>
       <c r="L52" t="n">
-        <v>970.562</v>
+        <v>974.4159999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10.86813569068909</v>
+        <v>7.304466009140015</v>
       </c>
       <c r="C2" t="n">
-        <v>6.846178770065308</v>
+        <v>12.40924024581909</v>
       </c>
       <c r="D2" t="n">
-        <v>6.460697650909424</v>
+        <v>9.726727247238159</v>
       </c>
       <c r="E2" t="n">
-        <v>6.942194938659668</v>
+        <v>9.15781569480896</v>
       </c>
       <c r="F2" t="n">
-        <v>7.158397674560547</v>
+        <v>8.411174297332764</v>
       </c>
       <c r="G2" t="n">
-        <v>8.925336122512817</v>
+        <v>9.153678417205811</v>
       </c>
       <c r="H2" t="n">
-        <v>6.769857883453369</v>
+        <v>6.60977578163147</v>
       </c>
       <c r="I2" t="n">
-        <v>8.463484525680542</v>
+        <v>7.817899703979492</v>
       </c>
       <c r="J2" t="n">
-        <v>6.687580347061157</v>
+        <v>7.30745792388916</v>
       </c>
       <c r="K2" t="n">
-        <v>9.47884726524353</v>
+        <v>9.963371753692627</v>
       </c>
       <c r="L2" t="n">
-        <v>7.860071086883545</v>
+        <v>8.786160707473755</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>10.31762957572937</v>
+        <v>9.925626754760742</v>
       </c>
       <c r="C3" t="n">
-        <v>7.15187406539917</v>
+        <v>15.21218776702881</v>
       </c>
       <c r="D3" t="n">
-        <v>7.089072942733765</v>
+        <v>11.91507840156555</v>
       </c>
       <c r="E3" t="n">
-        <v>8.127346038818359</v>
+        <v>8.538647174835205</v>
       </c>
       <c r="F3" t="n">
-        <v>7.399762153625488</v>
+        <v>7.224462270736694</v>
       </c>
       <c r="G3" t="n">
-        <v>10.04885768890381</v>
+        <v>8.970718860626221</v>
       </c>
       <c r="H3" t="n">
-        <v>7.588276386260986</v>
+        <v>8.246446132659912</v>
       </c>
       <c r="I3" t="n">
-        <v>7.386765956878662</v>
+        <v>7.28962230682373</v>
       </c>
       <c r="J3" t="n">
-        <v>7.17781662940979</v>
+        <v>7.017910957336426</v>
       </c>
       <c r="K3" t="n">
-        <v>7.944827079772949</v>
+        <v>8.092359304428101</v>
       </c>
       <c r="L3" t="n">
-        <v>8.023222851753236</v>
+        <v>9.243305993080138</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>8.645494937896729</v>
+        <v>8.164143800735474</v>
       </c>
       <c r="C4" t="n">
-        <v>9.424537420272827</v>
+        <v>8.174368143081665</v>
       </c>
       <c r="D4" t="n">
-        <v>7.425685405731201</v>
+        <v>10.95213222503662</v>
       </c>
       <c r="E4" t="n">
-        <v>7.084055423736572</v>
+        <v>6.862700939178467</v>
       </c>
       <c r="F4" t="n">
-        <v>9.106275320053101</v>
+        <v>7.253539800643921</v>
       </c>
       <c r="G4" t="n">
-        <v>7.765797853469849</v>
+        <v>9.788140296936035</v>
       </c>
       <c r="H4" t="n">
-        <v>9.644887924194336</v>
+        <v>7.077104330062866</v>
       </c>
       <c r="I4" t="n">
-        <v>8.365261316299438</v>
+        <v>9.250388145446777</v>
       </c>
       <c r="J4" t="n">
-        <v>7.198738574981689</v>
+        <v>9.445930957794189</v>
       </c>
       <c r="K4" t="n">
-        <v>9.415831565856934</v>
+        <v>12.50393581390381</v>
       </c>
       <c r="L4" t="n">
-        <v>8.407656574249268</v>
+        <v>8.947238445281982</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>7.213649749755859</v>
+        <v>11.72043824195862</v>
       </c>
       <c r="C5" t="n">
-        <v>6.544817447662354</v>
+        <v>8.124693632125854</v>
       </c>
       <c r="D5" t="n">
-        <v>6.441592216491699</v>
+        <v>11.36948800086975</v>
       </c>
       <c r="E5" t="n">
-        <v>6.334356307983398</v>
+        <v>7.998717546463013</v>
       </c>
       <c r="F5" t="n">
-        <v>6.563354253768921</v>
+        <v>9.906613111495972</v>
       </c>
       <c r="G5" t="n">
-        <v>7.427093267440796</v>
+        <v>7.39393424987793</v>
       </c>
       <c r="H5" t="n">
-        <v>6.550806045532227</v>
+        <v>7.117779970169067</v>
       </c>
       <c r="I5" t="n">
-        <v>6.138862371444702</v>
+        <v>8.556158304214478</v>
       </c>
       <c r="J5" t="n">
-        <v>6.667060852050781</v>
+        <v>8.406895399093628</v>
       </c>
       <c r="K5" t="n">
-        <v>5.938358068466187</v>
+        <v>6.941471099853516</v>
       </c>
       <c r="L5" t="n">
-        <v>6.581995058059692</v>
+        <v>8.753618955612183</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>6.558278799057007</v>
+        <v>6.48362398147583</v>
       </c>
       <c r="C6" t="n">
-        <v>5.743845224380493</v>
+        <v>8.097374677658081</v>
       </c>
       <c r="D6" t="n">
-        <v>6.82160472869873</v>
+        <v>6.298687934875488</v>
       </c>
       <c r="E6" t="n">
-        <v>6.754812240600586</v>
+        <v>5.996994256973267</v>
       </c>
       <c r="F6" t="n">
-        <v>8.95622706413269</v>
+        <v>6.341042280197144</v>
       </c>
       <c r="G6" t="n">
-        <v>6.821615934371948</v>
+        <v>6.327080726623535</v>
       </c>
       <c r="H6" t="n">
-        <v>6.58620285987854</v>
+        <v>5.714718103408813</v>
       </c>
       <c r="I6" t="n">
-        <v>5.947350263595581</v>
+        <v>8.347675561904907</v>
       </c>
       <c r="J6" t="n">
-        <v>6.111056089401245</v>
+        <v>8.987964153289795</v>
       </c>
       <c r="K6" t="n">
-        <v>8.673935413360596</v>
+        <v>8.684774875640869</v>
       </c>
       <c r="L6" t="n">
-        <v>6.897492861747741</v>
+        <v>7.127993655204773</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>8.556286573410034</v>
+        <v>7.61363959312439</v>
       </c>
       <c r="C7" t="n">
-        <v>10.28075480461121</v>
+        <v>8.444521188735962</v>
       </c>
       <c r="D7" t="n">
-        <v>8.34182071685791</v>
+        <v>9.007957220077515</v>
       </c>
       <c r="E7" t="n">
-        <v>8.757684707641602</v>
+        <v>9.067750692367554</v>
       </c>
       <c r="F7" t="n">
-        <v>9.384625196456909</v>
+        <v>9.662161588668823</v>
       </c>
       <c r="G7" t="n">
-        <v>9.433464050292969</v>
+        <v>8.536172389984131</v>
       </c>
       <c r="H7" t="n">
-        <v>7.769790887832642</v>
+        <v>8.275277137756348</v>
       </c>
       <c r="I7" t="n">
-        <v>8.369705200195312</v>
+        <v>11.75459575653076</v>
       </c>
       <c r="J7" t="n">
-        <v>9.267383575439453</v>
+        <v>7.377262353897095</v>
       </c>
       <c r="K7" t="n">
-        <v>7.170828342437744</v>
+        <v>7.585085153579712</v>
       </c>
       <c r="L7" t="n">
-        <v>8.733234405517578</v>
+        <v>8.73244230747223</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>6.999815702438354</v>
+        <v>8.007585763931274</v>
       </c>
       <c r="C8" t="n">
-        <v>7.245128154754639</v>
+        <v>8.380670070648193</v>
       </c>
       <c r="D8" t="n">
-        <v>8.376367807388306</v>
+        <v>8.443083524703979</v>
       </c>
       <c r="E8" t="n">
-        <v>9.266881704330444</v>
+        <v>8.444455146789551</v>
       </c>
       <c r="F8" t="n">
-        <v>7.368801355361938</v>
+        <v>10.0070903301239</v>
       </c>
       <c r="G8" t="n">
-        <v>8.247547388076782</v>
+        <v>8.511478662490845</v>
       </c>
       <c r="H8" t="n">
-        <v>7.911909103393555</v>
+        <v>8.785174369812012</v>
       </c>
       <c r="I8" t="n">
-        <v>9.927661895751953</v>
+        <v>10.84963774681091</v>
       </c>
       <c r="J8" t="n">
-        <v>9.349657535552979</v>
+        <v>8.279325723648071</v>
       </c>
       <c r="K8" t="n">
-        <v>7.243166208267212</v>
+        <v>13.94175100326538</v>
       </c>
       <c r="L8" t="n">
-        <v>8.193693685531617</v>
+        <v>9.365025234222411</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>9.421500205993652</v>
+        <v>10.45878434181213</v>
       </c>
       <c r="C9" t="n">
-        <v>7.438675880432129</v>
+        <v>12.32135152816772</v>
       </c>
       <c r="D9" t="n">
-        <v>8.199189424514771</v>
+        <v>12.40281510353088</v>
       </c>
       <c r="E9" t="n">
-        <v>7.976701736450195</v>
+        <v>12.30949759483337</v>
       </c>
       <c r="F9" t="n">
-        <v>8.782123327255249</v>
+        <v>11.48922443389893</v>
       </c>
       <c r="G9" t="n">
-        <v>8.684096574783325</v>
+        <v>11.32062292098999</v>
       </c>
       <c r="H9" t="n">
-        <v>9.315257549285889</v>
+        <v>12.06776165962219</v>
       </c>
       <c r="I9" t="n">
-        <v>8.749732971191406</v>
+        <v>8.152206897735596</v>
       </c>
       <c r="J9" t="n">
-        <v>7.251146078109741</v>
+        <v>10.14270853996277</v>
       </c>
       <c r="K9" t="n">
-        <v>7.833129644393921</v>
+        <v>8.441423654556274</v>
       </c>
       <c r="L9" t="n">
-        <v>8.365155339241028</v>
+        <v>10.91063966751099</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>8.686875820159912</v>
+        <v>7.412384271621704</v>
       </c>
       <c r="C10" t="n">
-        <v>6.719012260437012</v>
+        <v>10.63819336891174</v>
       </c>
       <c r="D10" t="n">
-        <v>7.662116765975952</v>
+        <v>12.21625328063965</v>
       </c>
       <c r="E10" t="n">
-        <v>9.188138246536255</v>
+        <v>9.773616075515747</v>
       </c>
       <c r="F10" t="n">
-        <v>7.169822454452515</v>
+        <v>10.83727836608887</v>
       </c>
       <c r="G10" t="n">
-        <v>6.505581617355347</v>
+        <v>12.0327889919281</v>
       </c>
       <c r="H10" t="n">
-        <v>9.160165071487427</v>
+        <v>10.66754198074341</v>
       </c>
       <c r="I10" t="n">
-        <v>6.375906229019165</v>
+        <v>10.16495513916016</v>
       </c>
       <c r="J10" t="n">
-        <v>6.815253257751465</v>
+        <v>9.117758989334106</v>
       </c>
       <c r="K10" t="n">
-        <v>6.188894510269165</v>
+        <v>10.74968576431274</v>
       </c>
       <c r="L10" t="n">
-        <v>7.447176623344421</v>
+        <v>10.36104562282562</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>6.657166004180908</v>
+        <v>11.81715488433838</v>
       </c>
       <c r="C11" t="n">
-        <v>7.276434898376465</v>
+        <v>7.557066679000854</v>
       </c>
       <c r="D11" t="n">
-        <v>8.928753137588501</v>
+        <v>13.82134604454041</v>
       </c>
       <c r="E11" t="n">
-        <v>9.047539710998535</v>
+        <v>9.833383798599243</v>
       </c>
       <c r="F11" t="n">
-        <v>6.476499319076538</v>
+        <v>9.976421356201172</v>
       </c>
       <c r="G11" t="n">
-        <v>7.813283681869507</v>
+        <v>8.158079862594604</v>
       </c>
       <c r="H11" t="n">
-        <v>8.258039712905884</v>
+        <v>10.89793300628662</v>
       </c>
       <c r="I11" t="n">
-        <v>9.172635316848755</v>
+        <v>8.520453453063965</v>
       </c>
       <c r="J11" t="n">
-        <v>6.869617462158203</v>
+        <v>9.935465574264526</v>
       </c>
       <c r="K11" t="n">
-        <v>6.897558927536011</v>
+        <v>7.111981153488159</v>
       </c>
       <c r="L11" t="n">
-        <v>7.73975281715393</v>
+        <v>9.762928581237793</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>9.508755445480347</v>
+        <v>11.36790180206299</v>
       </c>
       <c r="C12" t="n">
-        <v>9.284815311431885</v>
+        <v>11.67749238014221</v>
       </c>
       <c r="D12" t="n">
-        <v>10.18348550796509</v>
+        <v>10.57331085205078</v>
       </c>
       <c r="E12" t="n">
-        <v>7.28358793258667</v>
+        <v>10.39024829864502</v>
       </c>
       <c r="F12" t="n">
-        <v>8.20146632194519</v>
+        <v>10.06510734558105</v>
       </c>
       <c r="G12" t="n">
-        <v>9.976581573486328</v>
+        <v>10.35577368736267</v>
       </c>
       <c r="H12" t="n">
-        <v>11.53610396385193</v>
+        <v>7.812511205673218</v>
       </c>
       <c r="I12" t="n">
-        <v>10.89676427841187</v>
+        <v>8.939128398895264</v>
       </c>
       <c r="J12" t="n">
-        <v>7.623589992523193</v>
+        <v>10.14786219596863</v>
       </c>
       <c r="K12" t="n">
-        <v>10.30909705162048</v>
+        <v>11.41002321243286</v>
       </c>
       <c r="L12" t="n">
-        <v>9.480424737930297</v>
+        <v>10.27393593788147</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>8.816059350967407</v>
+        <v>6.552318572998047</v>
       </c>
       <c r="C13" t="n">
-        <v>6.834241390228271</v>
+        <v>8.512614250183105</v>
       </c>
       <c r="D13" t="n">
-        <v>8.394150495529175</v>
+        <v>7.913836240768433</v>
       </c>
       <c r="E13" t="n">
-        <v>7.131945610046387</v>
+        <v>7.379900693893433</v>
       </c>
       <c r="F13" t="n">
-        <v>6.275183200836182</v>
+        <v>8.735419988632202</v>
       </c>
       <c r="G13" t="n">
-        <v>7.556836605072021</v>
+        <v>6.844251155853271</v>
       </c>
       <c r="H13" t="n">
-        <v>6.342989683151245</v>
+        <v>8.564295768737793</v>
       </c>
       <c r="I13" t="n">
-        <v>7.99228572845459</v>
+        <v>8.447962522506714</v>
       </c>
       <c r="J13" t="n">
-        <v>6.270176649093628</v>
+        <v>7.107807874679565</v>
       </c>
       <c r="K13" t="n">
-        <v>6.923466920852661</v>
+        <v>8.405159950256348</v>
       </c>
       <c r="L13" t="n">
-        <v>7.253733563423157</v>
+        <v>7.846356701850891</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>7.395756721496582</v>
+        <v>13.80391931533813</v>
       </c>
       <c r="C14" t="n">
-        <v>8.790428876876831</v>
+        <v>8.510936975479126</v>
       </c>
       <c r="D14" t="n">
-        <v>8.009192943572998</v>
+        <v>8.190814733505249</v>
       </c>
       <c r="E14" t="n">
-        <v>9.622956991195679</v>
+        <v>8.013648748397827</v>
       </c>
       <c r="F14" t="n">
-        <v>9.467879772186279</v>
+        <v>7.916871786117554</v>
       </c>
       <c r="G14" t="n">
-        <v>7.635144710540771</v>
+        <v>7.130930423736572</v>
       </c>
       <c r="H14" t="n">
-        <v>8.080468416213989</v>
+        <v>7.733522176742554</v>
       </c>
       <c r="I14" t="n">
-        <v>8.880861043930054</v>
+        <v>7.479748725891113</v>
       </c>
       <c r="J14" t="n">
-        <v>7.576318025588989</v>
+        <v>8.113302946090698</v>
       </c>
       <c r="K14" t="n">
-        <v>9.941626787185669</v>
+        <v>9.523761987686157</v>
       </c>
       <c r="L14" t="n">
-        <v>8.540063428878785</v>
+        <v>8.641745781898498</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>7.322529554367065</v>
+        <v>10.21888756752014</v>
       </c>
       <c r="C15" t="n">
-        <v>7.103011608123779</v>
+        <v>8.209882497787476</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0197434425354</v>
+        <v>13.03715848922729</v>
       </c>
       <c r="E15" t="n">
-        <v>8.249547243118286</v>
+        <v>9.327995777130127</v>
       </c>
       <c r="F15" t="n">
-        <v>7.543363094329834</v>
+        <v>10.74534106254578</v>
       </c>
       <c r="G15" t="n">
-        <v>7.668075084686279</v>
+        <v>9.073766708374023</v>
       </c>
       <c r="H15" t="n">
-        <v>6.703067541122437</v>
+        <v>7.628471374511719</v>
       </c>
       <c r="I15" t="n">
-        <v>8.763564825057983</v>
+        <v>9.55469799041748</v>
       </c>
       <c r="J15" t="n">
-        <v>6.875485181808472</v>
+        <v>7.571802139282227</v>
       </c>
       <c r="K15" t="n">
-        <v>6.494943618774414</v>
+        <v>7.487433910369873</v>
       </c>
       <c r="L15" t="n">
-        <v>7.374333119392395</v>
+        <v>9.285543751716613</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>7.191671371459961</v>
+        <v>9.389592170715332</v>
       </c>
       <c r="C16" t="n">
-        <v>6.988190889358521</v>
+        <v>7.238893985748291</v>
       </c>
       <c r="D16" t="n">
-        <v>7.508350610733032</v>
+        <v>9.350666284561157</v>
       </c>
       <c r="E16" t="n">
-        <v>9.368640422821045</v>
+        <v>10.06198525428772</v>
       </c>
       <c r="F16" t="n">
-        <v>7.750745534896851</v>
+        <v>7.536844730377197</v>
       </c>
       <c r="G16" t="n">
-        <v>6.836065769195557</v>
+        <v>7.279533386230469</v>
       </c>
       <c r="H16" t="n">
-        <v>7.569186687469482</v>
+        <v>9.26821494102478</v>
       </c>
       <c r="I16" t="n">
-        <v>8.722294330596924</v>
+        <v>9.733969688415527</v>
       </c>
       <c r="J16" t="n">
-        <v>9.488304853439331</v>
+        <v>7.842935800552368</v>
       </c>
       <c r="K16" t="n">
-        <v>9.194062232971191</v>
+        <v>7.554796457290649</v>
       </c>
       <c r="L16" t="n">
-        <v>8.06175127029419</v>
+        <v>8.525743269920349</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>9.142210721969604</v>
+        <v>8.694747924804688</v>
       </c>
       <c r="C17" t="n">
-        <v>7.692903995513916</v>
+        <v>10.3001914024353</v>
       </c>
       <c r="D17" t="n">
-        <v>10.14065670967102</v>
+        <v>7.817457437515259</v>
       </c>
       <c r="E17" t="n">
-        <v>7.715867042541504</v>
+        <v>10.01471281051636</v>
       </c>
       <c r="F17" t="n">
-        <v>11.60639309883118</v>
+        <v>11.70672726631165</v>
       </c>
       <c r="G17" t="n">
-        <v>9.002546787261963</v>
+        <v>8.241959095001221</v>
       </c>
       <c r="H17" t="n">
-        <v>9.494299411773682</v>
+        <v>7.889899969100952</v>
       </c>
       <c r="I17" t="n">
-        <v>9.37511944770813</v>
+        <v>10.4531455039978</v>
       </c>
       <c r="J17" t="n">
-        <v>8.653957366943359</v>
+        <v>10.55009078979492</v>
       </c>
       <c r="K17" t="n">
-        <v>9.818973302841187</v>
+        <v>8.164050579071045</v>
       </c>
       <c r="L17" t="n">
-        <v>9.264292788505553</v>
+        <v>9.383298277854919</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>9.128233671188354</v>
+        <v>7.615633487701416</v>
       </c>
       <c r="C18" t="n">
-        <v>9.805006265640259</v>
+        <v>7.252005100250244</v>
       </c>
       <c r="D18" t="n">
-        <v>7.350779294967651</v>
+        <v>9.94739842414856</v>
       </c>
       <c r="E18" t="n">
-        <v>7.727806806564331</v>
+        <v>6.918498277664185</v>
       </c>
       <c r="F18" t="n">
-        <v>10.03093695640564</v>
+        <v>9.435501098632812</v>
       </c>
       <c r="G18" t="n">
-        <v>8.930736303329468</v>
+        <v>10.87444138526917</v>
       </c>
       <c r="H18" t="n">
-        <v>10.34411358833313</v>
+        <v>7.024296760559082</v>
       </c>
       <c r="I18" t="n">
-        <v>8.447504043579102</v>
+        <v>8.412821531295776</v>
       </c>
       <c r="J18" t="n">
-        <v>6.564305067062378</v>
+        <v>7.135902881622314</v>
       </c>
       <c r="K18" t="n">
-        <v>8.257985591888428</v>
+        <v>9.230361223220825</v>
       </c>
       <c r="L18" t="n">
-        <v>8.658740758895874</v>
+        <v>8.384686017036438</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>8.423545598983765</v>
+        <v>6.547234535217285</v>
       </c>
       <c r="C19" t="n">
-        <v>7.369244813919067</v>
+        <v>7.000317811965942</v>
       </c>
       <c r="D19" t="n">
-        <v>6.941790342330933</v>
+        <v>6.886774063110352</v>
       </c>
       <c r="E19" t="n">
-        <v>6.305447816848755</v>
+        <v>6.560487985610962</v>
       </c>
       <c r="F19" t="n">
-        <v>6.457535982131958</v>
+        <v>8.122738838195801</v>
       </c>
       <c r="G19" t="n">
-        <v>7.378207445144653</v>
+        <v>7.787227153778076</v>
       </c>
       <c r="H19" t="n">
-        <v>6.465521574020386</v>
+        <v>8.567090034484863</v>
       </c>
       <c r="I19" t="n">
-        <v>6.509912252426147</v>
+        <v>9.024525165557861</v>
       </c>
       <c r="J19" t="n">
-        <v>6.769738674163818</v>
+        <v>7.917826414108276</v>
       </c>
       <c r="K19" t="n">
-        <v>7.656519174575806</v>
+        <v>8.580055713653564</v>
       </c>
       <c r="L19" t="n">
-        <v>7.027746367454529</v>
+        <v>7.699427771568298</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>9.776596784591675</v>
+        <v>12.99239230155945</v>
       </c>
       <c r="C20" t="n">
-        <v>7.81810474395752</v>
+        <v>11.44841837882996</v>
       </c>
       <c r="D20" t="n">
-        <v>6.757797718048096</v>
+        <v>8.576065301895142</v>
       </c>
       <c r="E20" t="n">
-        <v>7.271470308303833</v>
+        <v>7.858300924301147</v>
       </c>
       <c r="F20" t="n">
-        <v>8.765735149383545</v>
+        <v>9.52169132232666</v>
       </c>
       <c r="G20" t="n">
-        <v>7.187174558639526</v>
+        <v>9.27181339263916</v>
       </c>
       <c r="H20" t="n">
-        <v>9.757145643234253</v>
+        <v>7.747429609298706</v>
       </c>
       <c r="I20" t="n">
-        <v>10.42046141624451</v>
+        <v>11.12040495872498</v>
       </c>
       <c r="J20" t="n">
-        <v>7.044042587280273</v>
+        <v>9.824558973312378</v>
       </c>
       <c r="K20" t="n">
-        <v>9.49630880355835</v>
+        <v>7.301100730895996</v>
       </c>
       <c r="L20" t="n">
-        <v>8.429483771324158</v>
+        <v>9.566217589378358</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>7.752729177474976</v>
+        <v>8.342689514160156</v>
       </c>
       <c r="C21" t="n">
-        <v>7.713824033737183</v>
+        <v>8.634381294250488</v>
       </c>
       <c r="D21" t="n">
-        <v>7.424084663391113</v>
+        <v>10.11802053451538</v>
       </c>
       <c r="E21" t="n">
-        <v>7.813056945800781</v>
+        <v>8.194281578063965</v>
       </c>
       <c r="F21" t="n">
-        <v>8.765685081481934</v>
+        <v>6.840874910354614</v>
       </c>
       <c r="G21" t="n">
-        <v>7.544124364852905</v>
+        <v>8.866289377212524</v>
       </c>
       <c r="H21" t="n">
-        <v>8.749234199523926</v>
+        <v>7.394099712371826</v>
       </c>
       <c r="I21" t="n">
-        <v>7.045029163360596</v>
+        <v>8.777553796768188</v>
       </c>
       <c r="J21" t="n">
-        <v>7.34526252746582</v>
+        <v>8.870843172073364</v>
       </c>
       <c r="K21" t="n">
-        <v>6.722363710403442</v>
+        <v>9.00640082359314</v>
       </c>
       <c r="L21" t="n">
-        <v>7.687539386749267</v>
+        <v>8.504543471336365</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>5.822153568267822</v>
+        <v>6.534826040267944</v>
       </c>
       <c r="C22" t="n">
-        <v>6.816673278808594</v>
+        <v>6.890604734420776</v>
       </c>
       <c r="D22" t="n">
-        <v>6.371495485305786</v>
+        <v>8.322532892227173</v>
       </c>
       <c r="E22" t="n">
-        <v>6.135817766189575</v>
+        <v>6.616445064544678</v>
       </c>
       <c r="F22" t="n">
-        <v>6.441605091094971</v>
+        <v>6.939442873001099</v>
       </c>
       <c r="G22" t="n">
-        <v>7.547327756881714</v>
+        <v>7.759159088134766</v>
       </c>
       <c r="H22" t="n">
-        <v>5.903441667556763</v>
+        <v>6.501999855041504</v>
       </c>
       <c r="I22" t="n">
-        <v>6.562274932861328</v>
+        <v>9.180482149124146</v>
       </c>
       <c r="J22" t="n">
-        <v>6.180758237838745</v>
+        <v>8.640849828720093</v>
       </c>
       <c r="K22" t="n">
-        <v>5.970806837081909</v>
+        <v>6.26128363609314</v>
       </c>
       <c r="L22" t="n">
-        <v>6.375235462188721</v>
+        <v>7.364762616157532</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>7.052539110183716</v>
+        <v>9.76108717918396</v>
       </c>
       <c r="C23" t="n">
-        <v>8.500343322753906</v>
+        <v>10.57751512527466</v>
       </c>
       <c r="D23" t="n">
-        <v>11.02490544319153</v>
+        <v>10.90387725830078</v>
       </c>
       <c r="E23" t="n">
-        <v>8.862914085388184</v>
+        <v>7.872949838638306</v>
       </c>
       <c r="F23" t="n">
-        <v>10.03542375564575</v>
+        <v>10.20045638084412</v>
       </c>
       <c r="G23" t="n">
-        <v>9.198575258255005</v>
+        <v>9.688835144042969</v>
       </c>
       <c r="H23" t="n">
-        <v>7.392687082290649</v>
+        <v>9.675117969512939</v>
       </c>
       <c r="I23" t="n">
-        <v>9.575595378875732</v>
+        <v>9.820090293884277</v>
       </c>
       <c r="J23" t="n">
-        <v>9.578592777252197</v>
+        <v>11.31239724159241</v>
       </c>
       <c r="K23" t="n">
-        <v>7.678409814834595</v>
+        <v>10.04716944694519</v>
       </c>
       <c r="L23" t="n">
-        <v>8.889998602867127</v>
+        <v>9.98594958782196</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>11.03688263893127</v>
+        <v>8.685131072998047</v>
       </c>
       <c r="C24" t="n">
-        <v>10.91577816009521</v>
+        <v>9.047871589660645</v>
       </c>
       <c r="D24" t="n">
-        <v>7.547808885574341</v>
+        <v>10.50122570991516</v>
       </c>
       <c r="E24" t="n">
-        <v>12.41084337234497</v>
+        <v>11.2330162525177</v>
       </c>
       <c r="F24" t="n">
-        <v>8.065009355545044</v>
+        <v>10.35540390014648</v>
       </c>
       <c r="G24" t="n">
-        <v>8.32427453994751</v>
+        <v>10.18351316452026</v>
       </c>
       <c r="H24" t="n">
-        <v>7.73085880279541</v>
+        <v>9.750959157943726</v>
       </c>
       <c r="I24" t="n">
-        <v>7.71682333946228</v>
+        <v>10.70254969596863</v>
       </c>
       <c r="J24" t="n">
-        <v>7.833027362823486</v>
+        <v>10.67451333999634</v>
       </c>
       <c r="K24" t="n">
-        <v>8.194127082824707</v>
+        <v>9.15850830078125</v>
       </c>
       <c r="L24" t="n">
-        <v>8.977543354034424</v>
+        <v>10.02926921844482</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>9.658870697021484</v>
+        <v>8.888230562210083</v>
       </c>
       <c r="C25" t="n">
-        <v>7.581204652786255</v>
+        <v>6.937719821929932</v>
       </c>
       <c r="D25" t="n">
-        <v>7.994606018066406</v>
+        <v>7.153388977050781</v>
       </c>
       <c r="E25" t="n">
-        <v>7.27597188949585</v>
+        <v>6.712001323699951</v>
       </c>
       <c r="F25" t="n">
-        <v>7.313860416412354</v>
+        <v>8.2788987159729</v>
       </c>
       <c r="G25" t="n">
-        <v>8.257954120635986</v>
+        <v>9.649196624755859</v>
       </c>
       <c r="H25" t="n">
-        <v>7.625560760498047</v>
+        <v>7.303153514862061</v>
       </c>
       <c r="I25" t="n">
-        <v>7.788162231445312</v>
+        <v>10.32562160491943</v>
       </c>
       <c r="J25" t="n">
-        <v>10.1426157951355</v>
+        <v>10.48699164390564</v>
       </c>
       <c r="K25" t="n">
-        <v>7.549278497695923</v>
+        <v>7.747282266616821</v>
       </c>
       <c r="L25" t="n">
-        <v>8.118808507919312</v>
+        <v>8.348248505592347</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>8.532743453979492</v>
+        <v>7.716365337371826</v>
       </c>
       <c r="C26" t="n">
-        <v>8.330771684646606</v>
+        <v>10.27352595329285</v>
       </c>
       <c r="D26" t="n">
-        <v>7.421086072921753</v>
+        <v>7.38714861869812</v>
       </c>
       <c r="E26" t="n">
-        <v>7.261504411697388</v>
+        <v>7.020266532897949</v>
       </c>
       <c r="F26" t="n">
-        <v>6.401687622070312</v>
+        <v>8.085377216339111</v>
       </c>
       <c r="G26" t="n">
-        <v>9.248401165008545</v>
+        <v>6.863645315170288</v>
       </c>
       <c r="H26" t="n">
-        <v>8.943749666213989</v>
+        <v>10.10809540748596</v>
       </c>
       <c r="I26" t="n">
-        <v>8.071943521499634</v>
+        <v>7.180510520935059</v>
       </c>
       <c r="J26" t="n">
-        <v>6.769256591796875</v>
+        <v>6.852709531784058</v>
       </c>
       <c r="K26" t="n">
-        <v>9.687819957733154</v>
+        <v>10.94531154632568</v>
       </c>
       <c r="L26" t="n">
-        <v>8.066896414756775</v>
+        <v>8.243295598030091</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>8.542726278305054</v>
+        <v>7.71472430229187</v>
       </c>
       <c r="C27" t="n">
-        <v>11.26476097106934</v>
+        <v>9.499746322631836</v>
       </c>
       <c r="D27" t="n">
-        <v>8.485370397567749</v>
+        <v>9.280182838439941</v>
       </c>
       <c r="E27" t="n">
-        <v>7.553795576095581</v>
+        <v>7.415224075317383</v>
       </c>
       <c r="F27" t="n">
-        <v>7.195660591125488</v>
+        <v>9.550103187561035</v>
       </c>
       <c r="G27" t="n">
-        <v>7.909348487854004</v>
+        <v>10.07608866691589</v>
       </c>
       <c r="H27" t="n">
-        <v>8.394129276275635</v>
+        <v>9.780784606933594</v>
       </c>
       <c r="I27" t="n">
-        <v>8.91977858543396</v>
+        <v>11.06733679771423</v>
       </c>
       <c r="J27" t="n">
-        <v>9.331717491149902</v>
+        <v>7.083089590072632</v>
       </c>
       <c r="K27" t="n">
-        <v>8.323289155960083</v>
+        <v>9.179452180862427</v>
       </c>
       <c r="L27" t="n">
-        <v>8.592057681083679</v>
+        <v>9.064673256874084</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>9.877826690673828</v>
+        <v>9.954570293426514</v>
       </c>
       <c r="C28" t="n">
-        <v>7.726789474487305</v>
+        <v>8.015564441680908</v>
       </c>
       <c r="D28" t="n">
-        <v>8.235998868942261</v>
+        <v>11.18708372116089</v>
       </c>
       <c r="E28" t="n">
-        <v>8.527758836746216</v>
+        <v>9.070743322372437</v>
       </c>
       <c r="F28" t="n">
-        <v>9.375099897384644</v>
+        <v>9.243342638015747</v>
       </c>
       <c r="G28" t="n">
-        <v>8.527767181396484</v>
+        <v>7.684469938278198</v>
       </c>
       <c r="H28" t="n">
-        <v>9.778058290481567</v>
+        <v>8.961070775985718</v>
       </c>
       <c r="I28" t="n">
-        <v>7.755748748779297</v>
+        <v>10.12981128692627</v>
       </c>
       <c r="J28" t="n">
-        <v>7.895056962966919</v>
+        <v>10.32450389862061</v>
       </c>
       <c r="K28" t="n">
-        <v>7.771681785583496</v>
+        <v>7.761292219161987</v>
       </c>
       <c r="L28" t="n">
-        <v>8.547178673744202</v>
+        <v>9.233245253562927</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>7.20964241027832</v>
+        <v>10.24248552322388</v>
       </c>
       <c r="C29" t="n">
-        <v>9.918228626251221</v>
+        <v>9.043887853622437</v>
       </c>
       <c r="D29" t="n">
-        <v>9.480864286422729</v>
+        <v>11.65088295936584</v>
       </c>
       <c r="E29" t="n">
-        <v>7.372251987457275</v>
+        <v>9.504502534866333</v>
       </c>
       <c r="F29" t="n">
-        <v>8.562715530395508</v>
+        <v>11.05443787574768</v>
       </c>
       <c r="G29" t="n">
-        <v>9.63641881942749</v>
+        <v>9.015488386154175</v>
       </c>
       <c r="H29" t="n">
-        <v>8.846440553665161</v>
+        <v>9.792840003967285</v>
       </c>
       <c r="I29" t="n">
-        <v>7.743333339691162</v>
+        <v>11.09164595603943</v>
       </c>
       <c r="J29" t="n">
-        <v>7.292423009872437</v>
+        <v>10.32952499389648</v>
       </c>
       <c r="K29" t="n">
-        <v>10.05835795402527</v>
+        <v>10.49922943115234</v>
       </c>
       <c r="L29" t="n">
-        <v>8.612067651748657</v>
+        <v>10.22249255180359</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>9.498164415359497</v>
+        <v>10.24530506134033</v>
       </c>
       <c r="C30" t="n">
-        <v>10.34653091430664</v>
+        <v>8.55914568901062</v>
       </c>
       <c r="D30" t="n">
-        <v>8.498456478118896</v>
+        <v>7.39564037322998</v>
       </c>
       <c r="E30" t="n">
-        <v>7.886636018753052</v>
+        <v>9.520565748214722</v>
       </c>
       <c r="F30" t="n">
-        <v>7.553254365921021</v>
+        <v>8.907734632492065</v>
       </c>
       <c r="G30" t="n">
-        <v>9.475842475891113</v>
+        <v>10.58438062667847</v>
       </c>
       <c r="H30" t="n">
-        <v>7.185678243637085</v>
+        <v>10.31437492370605</v>
       </c>
       <c r="I30" t="n">
-        <v>9.252411603927612</v>
+        <v>10.74343347549438</v>
       </c>
       <c r="J30" t="n">
-        <v>9.009104490280151</v>
+        <v>10.54210543632507</v>
       </c>
       <c r="K30" t="n">
-        <v>9.215495824813843</v>
+        <v>8.387570142745972</v>
       </c>
       <c r="L30" t="n">
-        <v>8.79215748310089</v>
+        <v>9.520025610923767</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>8.451961040496826</v>
+        <v>9.127068281173706</v>
       </c>
       <c r="C31" t="n">
-        <v>10.29272437095642</v>
+        <v>7.580167293548584</v>
       </c>
       <c r="D31" t="n">
-        <v>7.043575763702393</v>
+        <v>8.956623792648315</v>
       </c>
       <c r="E31" t="n">
-        <v>7.127360343933105</v>
+        <v>9.682213544845581</v>
       </c>
       <c r="F31" t="n">
-        <v>9.14320182800293</v>
+        <v>10.21970248222351</v>
       </c>
       <c r="G31" t="n">
-        <v>8.522798776626587</v>
+        <v>8.287923812866211</v>
       </c>
       <c r="H31" t="n">
-        <v>9.486302852630615</v>
+        <v>10.02020454406738</v>
       </c>
       <c r="I31" t="n">
-        <v>7.480933666229248</v>
+        <v>9.439419984817505</v>
       </c>
       <c r="J31" t="n">
-        <v>10.25534176826477</v>
+        <v>8.421507835388184</v>
       </c>
       <c r="K31" t="n">
-        <v>9.499762058258057</v>
+        <v>8.333032846450806</v>
       </c>
       <c r="L31" t="n">
-        <v>8.730396246910095</v>
+        <v>9.006786441802978</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>9.770584344863892</v>
+        <v>8.654855489730835</v>
       </c>
       <c r="C32" t="n">
-        <v>6.764781951904297</v>
+        <v>7.17765736579895</v>
       </c>
       <c r="D32" t="n">
-        <v>9.691339254379272</v>
+        <v>8.838441610336304</v>
       </c>
       <c r="E32" t="n">
-        <v>8.350283622741699</v>
+        <v>11.17923712730408</v>
       </c>
       <c r="F32" t="n">
-        <v>6.764277219772339</v>
+        <v>11.11427760124207</v>
       </c>
       <c r="G32" t="n">
-        <v>6.687457323074341</v>
+        <v>7.465036630630493</v>
       </c>
       <c r="H32" t="n">
-        <v>10.64184045791626</v>
+        <v>8.911136627197266</v>
       </c>
       <c r="I32" t="n">
-        <v>6.543868780136108</v>
+        <v>9.540290355682373</v>
       </c>
       <c r="J32" t="n">
-        <v>6.081989049911499</v>
+        <v>6.759072542190552</v>
       </c>
       <c r="K32" t="n">
-        <v>6.946828365325928</v>
+        <v>10.80443620681763</v>
       </c>
       <c r="L32" t="n">
-        <v>7.824325037002564</v>
+        <v>9.044444155693053</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>9.573146820068359</v>
+        <v>9.710871458053589</v>
       </c>
       <c r="C33" t="n">
-        <v>6.708727836608887</v>
+        <v>7.506118774414062</v>
       </c>
       <c r="D33" t="n">
-        <v>8.460460662841797</v>
+        <v>10.17578768730164</v>
       </c>
       <c r="E33" t="n">
-        <v>7.542801380157471</v>
+        <v>11.07916712760925</v>
       </c>
       <c r="F33" t="n">
-        <v>11.10765194892883</v>
+        <v>8.806483745574951</v>
       </c>
       <c r="G33" t="n">
-        <v>7.951842784881592</v>
+        <v>9.038280725479126</v>
       </c>
       <c r="H33" t="n">
-        <v>8.732498168945312</v>
+        <v>9.605961322784424</v>
       </c>
       <c r="I33" t="n">
-        <v>9.790645599365234</v>
+        <v>11.58357071876526</v>
       </c>
       <c r="J33" t="n">
-        <v>8.019993782043457</v>
+        <v>7.795154571533203</v>
       </c>
       <c r="K33" t="n">
-        <v>8.263842582702637</v>
+        <v>7.246189594268799</v>
       </c>
       <c r="L33" t="n">
-        <v>8.615161156654358</v>
+        <v>9.25475857257843</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>6.520404100418091</v>
+        <v>9.317750453948975</v>
       </c>
       <c r="C34" t="n">
-        <v>7.581841468811035</v>
+        <v>8.255921602249146</v>
       </c>
       <c r="D34" t="n">
-        <v>6.69806432723999</v>
+        <v>6.761917114257812</v>
       </c>
       <c r="E34" t="n">
-        <v>9.010646343231201</v>
+        <v>9.829122543334961</v>
       </c>
       <c r="F34" t="n">
-        <v>6.766895055770874</v>
+        <v>7.731324672698975</v>
       </c>
       <c r="G34" t="n">
-        <v>9.688289165496826</v>
+        <v>9.362948656082153</v>
       </c>
       <c r="H34" t="n">
-        <v>6.580917119979858</v>
+        <v>8.145035743713379</v>
       </c>
       <c r="I34" t="n">
-        <v>6.656661987304688</v>
+        <v>8.866214513778687</v>
       </c>
       <c r="J34" t="n">
-        <v>7.649071931838989</v>
+        <v>6.461030006408691</v>
       </c>
       <c r="K34" t="n">
-        <v>7.298532724380493</v>
+        <v>6.365222215652466</v>
       </c>
       <c r="L34" t="n">
-        <v>7.445132422447204</v>
+        <v>8.109648752212525</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>9.227975606918335</v>
+        <v>12.56340551376343</v>
       </c>
       <c r="C35" t="n">
-        <v>7.902930736541748</v>
+        <v>8.259363889694214</v>
       </c>
       <c r="D35" t="n">
-        <v>7.997255325317383</v>
+        <v>8.111167192459106</v>
       </c>
       <c r="E35" t="n">
-        <v>9.915688276290894</v>
+        <v>7.484386920928955</v>
       </c>
       <c r="F35" t="n">
-        <v>7.268590927124023</v>
+        <v>9.142985582351685</v>
       </c>
       <c r="G35" t="n">
-        <v>7.421688556671143</v>
+        <v>9.843901634216309</v>
       </c>
       <c r="H35" t="n">
-        <v>8.807608604431152</v>
+        <v>8.466250658035278</v>
       </c>
       <c r="I35" t="n">
-        <v>9.444930553436279</v>
+        <v>8.198743581771851</v>
       </c>
       <c r="J35" t="n">
-        <v>9.947623014450073</v>
+        <v>10.44155526161194</v>
       </c>
       <c r="K35" t="n">
-        <v>8.985924959182739</v>
+        <v>8.036797761917114</v>
       </c>
       <c r="L35" t="n">
-        <v>8.692021656036378</v>
+        <v>9.054855799674987</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>11.61736536026001</v>
+        <v>11.29579329490662</v>
       </c>
       <c r="C36" t="n">
-        <v>9.400673389434814</v>
+        <v>10.24859237670898</v>
       </c>
       <c r="D36" t="n">
-        <v>8.33477258682251</v>
+        <v>7.934780836105347</v>
       </c>
       <c r="E36" t="n">
-        <v>11.12714004516602</v>
+        <v>9.856633901596069</v>
       </c>
       <c r="F36" t="n">
-        <v>9.826932668685913</v>
+        <v>10.39239859580994</v>
       </c>
       <c r="G36" t="n">
-        <v>7.952274322509766</v>
+        <v>9.864331245422363</v>
       </c>
       <c r="H36" t="n">
-        <v>9.457884311676025</v>
+        <v>8.067502975463867</v>
       </c>
       <c r="I36" t="n">
-        <v>11.21340346336365</v>
+        <v>11.30504202842712</v>
       </c>
       <c r="J36" t="n">
-        <v>7.896387100219727</v>
+        <v>8.143989086151123</v>
       </c>
       <c r="K36" t="n">
-        <v>10.09777140617371</v>
+        <v>7.965758562088013</v>
       </c>
       <c r="L36" t="n">
-        <v>9.692460465431214</v>
+        <v>9.507482290267944</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>6.686493158340454</v>
+        <v>6.933458566665649</v>
       </c>
       <c r="C37" t="n">
-        <v>5.894948959350586</v>
+        <v>7.392231464385986</v>
       </c>
       <c r="D37" t="n">
-        <v>6.766779661178589</v>
+        <v>7.398818254470825</v>
       </c>
       <c r="E37" t="n">
-        <v>7.843041658401489</v>
+        <v>6.541676998138428</v>
       </c>
       <c r="F37" t="n">
-        <v>7.151257991790771</v>
+        <v>6.002946615219116</v>
       </c>
       <c r="G37" t="n">
-        <v>6.162314653396606</v>
+        <v>8.458427906036377</v>
       </c>
       <c r="H37" t="n">
-        <v>6.952880620956421</v>
+        <v>6.946846723556519</v>
       </c>
       <c r="I37" t="n">
-        <v>5.909451961517334</v>
+        <v>7.188081741333008</v>
       </c>
       <c r="J37" t="n">
-        <v>6.115916728973389</v>
+        <v>7.336409568786621</v>
       </c>
       <c r="K37" t="n">
-        <v>7.571723937988281</v>
+        <v>7.435945987701416</v>
       </c>
       <c r="L37" t="n">
-        <v>6.705480933189392</v>
+        <v>7.163484382629394</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>8.865910768508911</v>
+        <v>8.798019170761108</v>
       </c>
       <c r="C38" t="n">
-        <v>8.659924268722534</v>
+        <v>7.908978462219238</v>
       </c>
       <c r="D38" t="n">
-        <v>7.613590955734253</v>
+        <v>7.000050783157349</v>
       </c>
       <c r="E38" t="n">
-        <v>7.316843032836914</v>
+        <v>8.681653738021851</v>
       </c>
       <c r="F38" t="n">
-        <v>9.71076774597168</v>
+        <v>7.468064785003662</v>
       </c>
       <c r="G38" t="n">
-        <v>10.08227229118347</v>
+        <v>9.022880792617798</v>
       </c>
       <c r="H38" t="n">
-        <v>8.440483808517456</v>
+        <v>7.805757761001587</v>
       </c>
       <c r="I38" t="n">
-        <v>8.066532373428345</v>
+        <v>8.90360426902771</v>
       </c>
       <c r="J38" t="n">
-        <v>9.672855377197266</v>
+        <v>7.960748434066772</v>
       </c>
       <c r="K38" t="n">
-        <v>8.077399730682373</v>
+        <v>9.400413990020752</v>
       </c>
       <c r="L38" t="n">
-        <v>8.650658035278321</v>
+        <v>8.295017218589782</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>7.925639390945435</v>
+        <v>8.141668796539307</v>
       </c>
       <c r="C39" t="n">
-        <v>8.304383754730225</v>
+        <v>8.720871925354004</v>
       </c>
       <c r="D39" t="n">
-        <v>6.532355308532715</v>
+        <v>6.834712743759155</v>
       </c>
       <c r="E39" t="n">
-        <v>8.741211175918579</v>
+        <v>8.716331720352173</v>
       </c>
       <c r="F39" t="n">
-        <v>7.033109426498413</v>
+        <v>6.851718425750732</v>
       </c>
       <c r="G39" t="n">
-        <v>7.736795663833618</v>
+        <v>6.46172022819519</v>
       </c>
       <c r="H39" t="n">
-        <v>8.757171869277954</v>
+        <v>8.908177137374878</v>
       </c>
       <c r="I39" t="n">
-        <v>7.139298915863037</v>
+        <v>7.013245582580566</v>
       </c>
       <c r="J39" t="n">
-        <v>6.946811199188232</v>
+        <v>8.986967086791992</v>
       </c>
       <c r="K39" t="n">
-        <v>8.685360431671143</v>
+        <v>6.822754383087158</v>
       </c>
       <c r="L39" t="n">
-        <v>7.780213713645935</v>
+        <v>7.745816802978515</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>9.469851970672607</v>
+        <v>7.783836603164673</v>
       </c>
       <c r="C40" t="n">
-        <v>7.891414642333984</v>
+        <v>7.872668504714966</v>
       </c>
       <c r="D40" t="n">
-        <v>8.858438968658447</v>
+        <v>9.201423168182373</v>
       </c>
       <c r="E40" t="n">
-        <v>8.614056587219238</v>
+        <v>7.190861701965332</v>
       </c>
       <c r="F40" t="n">
-        <v>8.209089517593384</v>
+        <v>10.491943359375</v>
       </c>
       <c r="G40" t="n">
-        <v>8.135769844055176</v>
+        <v>7.49004602432251</v>
       </c>
       <c r="H40" t="n">
-        <v>10.12272191047668</v>
+        <v>7.595732927322388</v>
       </c>
       <c r="I40" t="n">
-        <v>6.868985891342163</v>
+        <v>7.873493432998657</v>
       </c>
       <c r="J40" t="n">
-        <v>6.467045545578003</v>
+        <v>8.61443042755127</v>
       </c>
       <c r="K40" t="n">
-        <v>8.926758289337158</v>
+        <v>9.555247783660889</v>
       </c>
       <c r="L40" t="n">
-        <v>8.356413316726684</v>
+        <v>8.366968393325806</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>8.558724403381348</v>
+        <v>11.27285480499268</v>
       </c>
       <c r="C41" t="n">
-        <v>9.199535369873047</v>
+        <v>9.233866453170776</v>
       </c>
       <c r="D41" t="n">
-        <v>9.254408597946167</v>
+        <v>8.182216882705688</v>
       </c>
       <c r="E41" t="n">
-        <v>7.493416309356689</v>
+        <v>10.50191235542297</v>
       </c>
       <c r="F41" t="n">
-        <v>9.743690490722656</v>
+        <v>10.84225344657898</v>
       </c>
       <c r="G41" t="n">
-        <v>9.410012483596802</v>
+        <v>7.962737560272217</v>
       </c>
       <c r="H41" t="n">
-        <v>10.41050148010254</v>
+        <v>11.04760503768921</v>
       </c>
       <c r="I41" t="n">
-        <v>9.526250123977661</v>
+        <v>8.709305286407471</v>
       </c>
       <c r="J41" t="n">
-        <v>11.01094079017639</v>
+        <v>11.48277568817139</v>
       </c>
       <c r="K41" t="n">
-        <v>7.694888830184937</v>
+        <v>11.89717984199524</v>
       </c>
       <c r="L41" t="n">
-        <v>9.230236887931824</v>
+        <v>10.11327073574066</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.569304466247559</v>
+        <v>5.955074787139893</v>
       </c>
       <c r="C42" t="n">
-        <v>5.347378730773926</v>
+        <v>8.442423820495605</v>
       </c>
       <c r="D42" t="n">
-        <v>6.120900392532349</v>
+        <v>8.497433185577393</v>
       </c>
       <c r="E42" t="n">
-        <v>5.995261430740356</v>
+        <v>8.1372389793396</v>
       </c>
       <c r="F42" t="n">
-        <v>5.844623327255249</v>
+        <v>6.75992226600647</v>
       </c>
       <c r="G42" t="n">
-        <v>6.104211330413818</v>
+        <v>10.8011155128479</v>
       </c>
       <c r="H42" t="n">
-        <v>6.670636415481567</v>
+        <v>6.782860994338989</v>
       </c>
       <c r="I42" t="n">
-        <v>5.73566198348999</v>
+        <v>7.139906644821167</v>
       </c>
       <c r="J42" t="n">
-        <v>5.337125539779663</v>
+        <v>6.695095777511597</v>
       </c>
       <c r="K42" t="n">
-        <v>5.7056565284729</v>
+        <v>6.329074382781982</v>
       </c>
       <c r="L42" t="n">
-        <v>5.843076014518738</v>
+        <v>7.55401463508606</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>6.922516584396362</v>
+        <v>6.590375900268555</v>
       </c>
       <c r="C43" t="n">
-        <v>7.507575273513794</v>
+        <v>8.862300157546997</v>
       </c>
       <c r="D43" t="n">
-        <v>6.47649359703064</v>
+        <v>8.570081949234009</v>
       </c>
       <c r="E43" t="n">
-        <v>7.630560636520386</v>
+        <v>6.95639705657959</v>
       </c>
       <c r="F43" t="n">
-        <v>8.419808387756348</v>
+        <v>8.640892744064331</v>
       </c>
       <c r="G43" t="n">
-        <v>8.156791210174561</v>
+        <v>8.989968299865723</v>
       </c>
       <c r="H43" t="n">
-        <v>7.203645706176758</v>
+        <v>7.035187244415283</v>
       </c>
       <c r="I43" t="n">
-        <v>6.592332363128662</v>
+        <v>8.642886400222778</v>
       </c>
       <c r="J43" t="n">
-        <v>6.05177640914917</v>
+        <v>9.09966516494751</v>
       </c>
       <c r="K43" t="n">
-        <v>6.761884927749634</v>
+        <v>7.695420503616333</v>
       </c>
       <c r="L43" t="n">
-        <v>7.172338509559632</v>
+        <v>8.108317542076112</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>7.784571170806885</v>
+        <v>10.6176061630249</v>
       </c>
       <c r="C44" t="n">
-        <v>7.414113759994507</v>
+        <v>7.013244390487671</v>
       </c>
       <c r="D44" t="n">
-        <v>7.287981986999512</v>
+        <v>7.228669166564941</v>
       </c>
       <c r="E44" t="n">
-        <v>8.840347528457642</v>
+        <v>7.551804065704346</v>
       </c>
       <c r="F44" t="n">
-        <v>7.774953365325928</v>
+        <v>10.44606471061707</v>
       </c>
       <c r="G44" t="n">
-        <v>9.011106491088867</v>
+        <v>8.05745267868042</v>
       </c>
       <c r="H44" t="n">
-        <v>7.558877944946289</v>
+        <v>7.798145771026611</v>
       </c>
       <c r="I44" t="n">
-        <v>7.342451095581055</v>
+        <v>9.43377161026001</v>
       </c>
       <c r="J44" t="n">
-        <v>10.22433948516846</v>
+        <v>7.445090293884277</v>
       </c>
       <c r="K44" t="n">
-        <v>9.128605127334595</v>
+        <v>7.025213003158569</v>
       </c>
       <c r="L44" t="n">
-        <v>8.236734795570374</v>
+        <v>8.261706185340881</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>7.508505821228027</v>
+        <v>10.44107818603516</v>
       </c>
       <c r="C45" t="n">
-        <v>9.260015726089478</v>
+        <v>11.30177664756775</v>
       </c>
       <c r="D45" t="n">
-        <v>7.937938451766968</v>
+        <v>11.18508887290955</v>
       </c>
       <c r="E45" t="n">
-        <v>7.375640153884888</v>
+        <v>10.04414010047913</v>
       </c>
       <c r="F45" t="n">
-        <v>9.191860914230347</v>
+        <v>8.326050996780396</v>
       </c>
       <c r="G45" t="n">
-        <v>9.126081228256226</v>
+        <v>9.93247652053833</v>
       </c>
       <c r="H45" t="n">
-        <v>8.346644163131714</v>
+        <v>10.02592062950134</v>
       </c>
       <c r="I45" t="n">
-        <v>9.882967472076416</v>
+        <v>10.79225397109985</v>
       </c>
       <c r="J45" t="n">
-        <v>9.029804944992065</v>
+        <v>9.637287616729736</v>
       </c>
       <c r="K45" t="n">
-        <v>11.10405158996582</v>
+        <v>9.736961364746094</v>
       </c>
       <c r="L45" t="n">
-        <v>8.876351046562196</v>
+        <v>10.14230349063873</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>10.01594662666321</v>
+        <v>7.739050149917603</v>
       </c>
       <c r="C46" t="n">
-        <v>8.071499109268188</v>
+        <v>9.031301736831665</v>
       </c>
       <c r="D46" t="n">
-        <v>9.801234722137451</v>
+        <v>10.06030797958374</v>
       </c>
       <c r="E46" t="n">
-        <v>8.574490308761597</v>
+        <v>7.239639520645142</v>
       </c>
       <c r="F46" t="n">
-        <v>9.016732215881348</v>
+        <v>8.06842303276062</v>
       </c>
       <c r="G46" t="n">
-        <v>7.663484811782837</v>
+        <v>9.815413475036621</v>
       </c>
       <c r="H46" t="n">
-        <v>6.707431316375732</v>
+        <v>9.556522607803345</v>
       </c>
       <c r="I46" t="n">
-        <v>8.315319538116455</v>
+        <v>8.393592119216919</v>
       </c>
       <c r="J46" t="n">
-        <v>9.571135759353638</v>
+        <v>10.06518507003784</v>
       </c>
       <c r="K46" t="n">
-        <v>6.894966602325439</v>
+        <v>8.244352340698242</v>
       </c>
       <c r="L46" t="n">
-        <v>8.46322410106659</v>
+        <v>8.821378803253173</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>10.62494730949402</v>
+        <v>7.788172483444214</v>
       </c>
       <c r="C47" t="n">
-        <v>8.025549411773682</v>
+        <v>9.118290901184082</v>
       </c>
       <c r="D47" t="n">
-        <v>8.330749034881592</v>
+        <v>10.5755033493042</v>
       </c>
       <c r="E47" t="n">
-        <v>10.42129230499268</v>
+        <v>7.951371908187866</v>
       </c>
       <c r="F47" t="n">
-        <v>9.234417915344238</v>
+        <v>9.189530611038208</v>
       </c>
       <c r="G47" t="n">
-        <v>9.029819250106812</v>
+        <v>8.792198896408081</v>
       </c>
       <c r="H47" t="n">
-        <v>8.0127854347229</v>
+        <v>9.650237798690796</v>
       </c>
       <c r="I47" t="n">
-        <v>8.224822044372559</v>
+        <v>8.939312219619751</v>
       </c>
       <c r="J47" t="n">
-        <v>7.669806003570557</v>
+        <v>9.776853799819946</v>
       </c>
       <c r="K47" t="n">
-        <v>10.00663495063782</v>
+        <v>10.31042861938477</v>
       </c>
       <c r="L47" t="n">
-        <v>8.958082365989686</v>
+        <v>9.209190058708192</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>9.722498416900635</v>
+        <v>6.595362901687622</v>
       </c>
       <c r="C48" t="n">
-        <v>9.852818965911865</v>
+        <v>7.600673675537109</v>
       </c>
       <c r="D48" t="n">
-        <v>8.91473388671875</v>
+        <v>8.495429992675781</v>
       </c>
       <c r="E48" t="n">
-        <v>7.421868801116943</v>
+        <v>9.885448932647705</v>
       </c>
       <c r="F48" t="n">
-        <v>9.51036548614502</v>
+        <v>10.28120827674866</v>
       </c>
       <c r="G48" t="n">
-        <v>9.051141262054443</v>
+        <v>8.584604263305664</v>
       </c>
       <c r="H48" t="n">
-        <v>7.678818702697754</v>
+        <v>7.508479118347168</v>
       </c>
       <c r="I48" t="n">
-        <v>9.043837308883667</v>
+        <v>7.320908308029175</v>
       </c>
       <c r="J48" t="n">
-        <v>9.73967432975769</v>
+        <v>8.819665193557739</v>
       </c>
       <c r="K48" t="n">
-        <v>7.016151428222656</v>
+        <v>9.29328441619873</v>
       </c>
       <c r="L48" t="n">
-        <v>8.795190858840943</v>
+        <v>8.438506507873536</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>8.401668310165405</v>
+        <v>9.924459934234619</v>
       </c>
       <c r="C49" t="n">
-        <v>9.31774640083313</v>
+        <v>9.400859832763672</v>
       </c>
       <c r="D49" t="n">
-        <v>9.619504451751709</v>
+        <v>8.597009658813477</v>
       </c>
       <c r="E49" t="n">
-        <v>9.559758424758911</v>
+        <v>10.87037301063538</v>
       </c>
       <c r="F49" t="n">
-        <v>8.032671451568604</v>
+        <v>8.059668302536011</v>
       </c>
       <c r="G49" t="n">
-        <v>9.667460441589355</v>
+        <v>7.83160924911499</v>
       </c>
       <c r="H49" t="n">
-        <v>10.29733896255493</v>
+        <v>9.118854761123657</v>
       </c>
       <c r="I49" t="n">
-        <v>8.110424280166626</v>
+        <v>7.943325757980347</v>
       </c>
       <c r="J49" t="n">
-        <v>8.321310758590698</v>
+        <v>11.62396740913391</v>
       </c>
       <c r="K49" t="n">
-        <v>8.039243936538696</v>
+        <v>10.53646445274353</v>
       </c>
       <c r="L49" t="n">
-        <v>8.936712741851807</v>
+        <v>9.390659236907959</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>9.830295324325562</v>
+        <v>9.617279052734375</v>
       </c>
       <c r="C50" t="n">
-        <v>9.72702693939209</v>
+        <v>9.192600250244141</v>
       </c>
       <c r="D50" t="n">
-        <v>10.9608473777771</v>
+        <v>11.29797339439392</v>
       </c>
       <c r="E50" t="n">
-        <v>8.504327774047852</v>
+        <v>7.257639408111572</v>
       </c>
       <c r="F50" t="n">
-        <v>7.70159387588501</v>
+        <v>10.99958467483521</v>
       </c>
       <c r="G50" t="n">
-        <v>10.88274955749512</v>
+        <v>8.834375143051147</v>
       </c>
       <c r="H50" t="n">
-        <v>9.539555072784424</v>
+        <v>10.99107241630554</v>
       </c>
       <c r="I50" t="n">
-        <v>9.463468074798584</v>
+        <v>11.01693391799927</v>
       </c>
       <c r="J50" t="n">
-        <v>7.908446073532104</v>
+        <v>9.217350482940674</v>
       </c>
       <c r="K50" t="n">
-        <v>7.584902286529541</v>
+        <v>9.867242813110352</v>
       </c>
       <c r="L50" t="n">
-        <v>9.210321235656739</v>
+        <v>9.82920515537262</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>7.712238073348999</v>
+        <v>8.010584592819214</v>
       </c>
       <c r="C51" t="n">
-        <v>9.737392425537109</v>
+        <v>10.20770263671875</v>
       </c>
       <c r="D51" t="n">
-        <v>9.496420621871948</v>
+        <v>8.764561653137207</v>
       </c>
       <c r="E51" t="n">
-        <v>9.458704233169556</v>
+        <v>9.460821390151978</v>
       </c>
       <c r="F51" t="n">
-        <v>8.74230170249939</v>
+        <v>8.753381490707397</v>
       </c>
       <c r="G51" t="n">
-        <v>7.352560043334961</v>
+        <v>9.320110559463501</v>
       </c>
       <c r="H51" t="n">
-        <v>10.32103776931763</v>
+        <v>9.667081594467163</v>
       </c>
       <c r="I51" t="n">
-        <v>8.655812978744507</v>
+        <v>8.833627223968506</v>
       </c>
       <c r="J51" t="n">
-        <v>9.615322589874268</v>
+        <v>10.41219544410706</v>
       </c>
       <c r="K51" t="n">
-        <v>7.919301986694336</v>
+        <v>10.0903913974762</v>
       </c>
       <c r="L51" t="n">
-        <v>8.90110924243927</v>
+        <v>9.352045798301697</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>8.527500395774842</v>
+        <v>9.021090335845948</v>
       </c>
       <c r="C52" t="n">
-        <v>8.166702308654784</v>
+        <v>8.946359901428222</v>
       </c>
       <c r="D52" t="n">
-        <v>8.054707407951355</v>
+        <v>9.300300679206849</v>
       </c>
       <c r="E52" t="n">
-        <v>8.162445449829102</v>
+        <v>8.675348520278931</v>
       </c>
       <c r="F52" t="n">
-        <v>8.207398447990418</v>
+        <v>9.058803000450133</v>
       </c>
       <c r="G52" t="n">
-        <v>8.306219973564147</v>
+        <v>8.832820358276367</v>
       </c>
       <c r="H52" t="n">
-        <v>8.342510223388672</v>
+        <v>8.618646292686462</v>
       </c>
       <c r="I52" t="n">
-        <v>8.18690589427948</v>
+        <v>9.199331254959107</v>
       </c>
       <c r="J52" t="n">
-        <v>7.903435244560241</v>
+        <v>8.850885920524597</v>
       </c>
       <c r="K52" t="n">
-        <v>8.165203676223754</v>
+        <v>8.873157916069031</v>
       </c>
       <c r="L52" t="n">
-        <v>8.202302902221678</v>
+        <v>8.937674417972564</v>
       </c>
     </row>
   </sheetData>
